--- a/data/leagues/Game of Yards! 2026.xlsx
+++ b/data/leagues/Game of Yards! 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="100">
   <si>
     <t>Groot-o-Matic</t>
   </si>
@@ -55,10 +55,13 @@
     <t>Team HebAchi</t>
   </si>
   <si>
-    <t>1-0-0</t>
-  </si>
-  <si>
-    <t>0-1-0</t>
+    <t>1-1-0</t>
+  </si>
+  <si>
+    <t>0-2-0</t>
+  </si>
+  <si>
+    <t>2-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -118,6 +121,9 @@
     <t>Week_2</t>
   </si>
   <si>
+    <t>Week_3</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -142,33 +148,33 @@
     <t>Prahlad Singh</t>
   </si>
   <si>
+    <t>Shihab Chowdhury</t>
+  </si>
+  <si>
     <t>Hayat Khan</t>
   </si>
   <si>
+    <t>Kabir Manocha</t>
+  </si>
+  <si>
+    <t>Vidhi Sethia</t>
+  </si>
+  <si>
+    <t>Pawan Bhambhwani</t>
+  </si>
+  <si>
+    <t>Achira Amur</t>
+  </si>
+  <si>
+    <t>Saurin Sethia</t>
+  </si>
+  <si>
     <t>Harshit Aggarwal</t>
   </si>
   <si>
-    <t>Shihab Chowdhury</t>
-  </si>
-  <si>
-    <t>Saurin Sethia</t>
-  </si>
-  <si>
-    <t>Kabir Manocha</t>
-  </si>
-  <si>
-    <t>Achira Amur</t>
-  </si>
-  <si>
-    <t>Pawan Bhambhwani</t>
-  </si>
-  <si>
     <t>Utkarsh Gupta</t>
   </si>
   <si>
-    <t>Vidhi Sethia</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -193,66 +199,66 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>11.4-2.5-0.1</t>
-  </si>
-  <si>
-    <t>10.2-3.7-0.1</t>
-  </si>
-  <si>
-    <t>8.6-5.3-0.1</t>
-  </si>
-  <si>
-    <t>8.3-5.6-0.1</t>
-  </si>
-  <si>
-    <t>7.4-6.5-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.7-0.1</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>5.0-8.9-0.1</t>
-  </si>
-  <si>
-    <t>2.9-11.0-0.1</t>
-  </si>
-  <si>
-    <t>1.7-12.2-0.1</t>
-  </si>
-  <si>
-    <t>12-2</t>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>11.2-2.7-0.1</t>
+  </si>
+  <si>
+    <t>10.4-3.4-0.1</t>
+  </si>
+  <si>
+    <t>8.9-5.0-0.1</t>
+  </si>
+  <si>
+    <t>8.4-5.6-0.1</t>
+  </si>
+  <si>
+    <t>6.4-7.5-0.1</t>
+  </si>
+  <si>
+    <t>5.7-8.1-0.1</t>
+  </si>
+  <si>
+    <t>6.1-7.8-0.1</t>
+  </si>
+  <si>
+    <t>4.7-9.2-0.1</t>
+  </si>
+  <si>
+    <t>4.2-9.7-0.1</t>
+  </si>
+  <si>
+    <t>3.5-10.5-0.1</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
-    <t>8-6</t>
-  </si>
-  <si>
     <t>9-5</t>
   </si>
   <si>
     <t>7-7</t>
   </si>
   <si>
+    <t>6-8</t>
+  </si>
+  <si>
     <t>5-9</t>
   </si>
   <si>
+    <t>4-10</t>
+  </si>
+  <si>
     <t>3-11</t>
   </si>
   <si>
-    <t>1-13</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -262,7 +268,40 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↑9</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↓9</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↓11</t>
+  </si>
+  <si>
+    <t>↓4</t>
+  </si>
+  <si>
     <t>Week 1</t>
+  </si>
+  <si>
+    <t>Week 2</t>
   </si>
   <si>
     <t>Week</t>
@@ -690,7 +729,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -702,10 +741,10 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -725,7 +764,7 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -740,7 +779,7 @@
         <v>11</v>
       </c>
       <c r="J3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K3" t="s">
         <v>11</v>
@@ -760,7 +799,7 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -772,13 +811,13 @@
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -824,31 +863,31 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
       </c>
       <c r="I6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -859,31 +898,31 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
       </c>
       <c r="I7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -894,31 +933,31 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -929,31 +968,31 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H9" t="s">
         <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -970,7 +1009,7 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -985,7 +1024,7 @@
         <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K10" t="s">
         <v>11</v>
@@ -996,34 +1035,34 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1033,30 +1072,56 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>86</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>-8</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1071,13 +1136,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1085,10 +1150,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -1099,13 +1164,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1116,7 +1181,7 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1127,13 +1192,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1141,10 +1206,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -1155,13 +1220,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1169,13 +1234,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1183,10 +1248,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1197,10 +1262,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1211,13 +1276,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1232,16 +1297,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1249,16 +1314,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1266,16 +1331,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="D3">
-        <v>-0.09999999999999998</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1283,16 +1348,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D4">
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1300,13 +1365,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="D5">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1320,10 +1385,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -1334,13 +1399,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="D7">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -1351,16 +1416,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="D8">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1368,13 +1433,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D9">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -1385,16 +1450,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1402,13 +1467,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -1426,66 +1491,66 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>69</v>
+        <v>62.9</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="E2">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="F2">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1497,36 +1562,36 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3">
+        <v>25.8</v>
+      </c>
+      <c r="C3">
+        <v>42.7</v>
+      </c>
+      <c r="D3">
         <v>21.5</v>
       </c>
-      <c r="C3">
-        <v>42.2</v>
-      </c>
-      <c r="D3">
-        <v>17.9</v>
-      </c>
       <c r="E3">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F3">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="G3">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="H3">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="I3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1535,240 +1600,240 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="C4">
-        <v>13.1</v>
+        <v>16</v>
       </c>
       <c r="D4">
-        <v>24.5</v>
+        <v>31.2</v>
       </c>
       <c r="E4">
-        <v>22.5</v>
+        <v>24.4</v>
       </c>
       <c r="F4">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="G4">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>1.9</v>
       </c>
       <c r="I4">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0.1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
-        <v>90.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="C5">
-        <v>12.5</v>
+        <v>14.1</v>
       </c>
       <c r="D5">
-        <v>20.8</v>
+        <v>26.6</v>
       </c>
       <c r="E5">
-        <v>21.1</v>
+        <v>28.6</v>
       </c>
       <c r="F5">
-        <v>20.7</v>
+        <v>12.9</v>
       </c>
       <c r="G5">
-        <v>12.8</v>
+        <v>7.8</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="I5">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J5">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L5">
-        <v>90.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="D6">
-        <v>13.4</v>
+        <v>5.3</v>
       </c>
       <c r="E6">
-        <v>16.9</v>
+        <v>15.7</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>25.8</v>
       </c>
       <c r="G6">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="H6">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="I6">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="L6">
-        <v>77.2</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B7">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="D7">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="E7">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="F7">
-        <v>16.6</v>
+        <v>15.6</v>
       </c>
       <c r="G7">
-        <v>23.2</v>
+        <v>24.1</v>
       </c>
       <c r="H7">
-        <v>21.4</v>
+        <v>20.3</v>
       </c>
       <c r="I7">
-        <v>9.800000000000001</v>
+        <v>14.9</v>
       </c>
       <c r="J7">
-        <v>1.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K7">
-        <v>0.1</v>
+        <v>3.2</v>
       </c>
       <c r="L7">
-        <v>67.40000000000001</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="D8">
-        <v>6.6</v>
+        <v>2.9</v>
       </c>
       <c r="E8">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="F8">
-        <v>16.7</v>
+        <v>19.6</v>
       </c>
       <c r="G8">
-        <v>20.1</v>
+        <v>21.1</v>
       </c>
       <c r="H8">
-        <v>25.9</v>
+        <v>20.4</v>
       </c>
       <c r="I8">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>8.6</v>
       </c>
       <c r="K8">
-        <v>0.1</v>
+        <v>3.9</v>
       </c>
       <c r="L8">
-        <v>58</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D9">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>9.199999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="H9">
-        <v>19.5</v>
+        <v>18.8</v>
       </c>
       <c r="I9">
-        <v>51.2</v>
+        <v>25.2</v>
       </c>
       <c r="J9">
-        <v>11.2</v>
+        <v>20.3</v>
       </c>
       <c r="K9">
-        <v>1.4</v>
+        <v>14.2</v>
       </c>
       <c r="L9">
-        <v>16.7</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1777,36 +1842,36 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="G10">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>13.4</v>
       </c>
       <c r="I10">
-        <v>11.5</v>
+        <v>20.5</v>
       </c>
       <c r="J10">
-        <v>58.2</v>
+        <v>30.3</v>
       </c>
       <c r="K10">
-        <v>27.5</v>
+        <v>24.4</v>
       </c>
       <c r="L10">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1818,28 +1883,28 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H11">
-        <v>0.1</v>
+        <v>5.7</v>
       </c>
       <c r="I11">
+        <v>12.9</v>
+      </c>
+      <c r="J11">
+        <v>25.7</v>
+      </c>
+      <c r="K11">
+        <v>52.7</v>
+      </c>
+      <c r="L11">
         <v>3</v>
-      </c>
-      <c r="J11">
-        <v>26</v>
-      </c>
-      <c r="K11">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1849,125 +1914,158 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>99.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>90.7</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>99.5</v>
-      </c>
-      <c r="C3">
-        <v>98.90000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="B4">
-        <v>92.60000000000001</v>
+        <v>99</v>
       </c>
       <c r="C4">
-        <v>92.30000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>96.8</v>
+      </c>
+      <c r="D4">
+        <v>97.39999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>90</v>
+        <v>99.8</v>
       </c>
       <c r="C5">
-        <v>88.90000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="D5">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>14.6</v>
+      </c>
+      <c r="C6">
+        <v>65.2</v>
+      </c>
+      <c r="D6">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B6">
-        <v>77.10000000000001</v>
-      </c>
-      <c r="C6">
-        <v>75.40000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
+      <c r="B7">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="C7">
+        <v>57.4</v>
+      </c>
+      <c r="D7">
+        <v>53.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="C7">
-        <v>68.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
+      <c r="B8">
+        <v>66</v>
+      </c>
+      <c r="C8">
+        <v>53.2</v>
+      </c>
+      <c r="D8">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B8">
-        <v>58.5</v>
-      </c>
-      <c r="C8">
-        <v>59.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B9">
-        <v>14.5</v>
+        <v>59.4</v>
       </c>
       <c r="C9">
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>20.6</v>
+      </c>
+      <c r="D9">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>11.6</v>
+      </c>
+      <c r="D10">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>3.3</v>
+      </c>
+      <c r="D11">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
@@ -1982,28 +2080,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2014,25 +2112,25 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>74.45</v>
+        <v>90.45</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>125.42</v>
+        <v>119.08</v>
       </c>
       <c r="G2">
-        <v>0.615</v>
+        <v>0.583</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2040,28 +2138,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>74.98</v>
+        <v>98.89</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>122.56</v>
+        <v>112.82</v>
       </c>
       <c r="G3">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2069,28 +2167,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>108.34</v>
+        <v>84.03</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>121.12</v>
+        <v>114.47</v>
       </c>
       <c r="G4">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H4">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2098,28 +2196,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>119.32</v>
+        <v>113.25</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5">
-        <v>115.49</v>
+        <v>113.86</v>
       </c>
       <c r="G5">
-        <v>0.538</v>
+        <v>0.625</v>
       </c>
       <c r="H5">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2127,28 +2225,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>126.24</v>
+        <v>120.72</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>113.38</v>
+        <v>112.95</v>
       </c>
       <c r="G6">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="H6">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2156,28 +2254,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>125.15</v>
+        <v>101.95</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>115.25</v>
+        <v>111.48</v>
       </c>
       <c r="G7">
-        <v>0.538</v>
+        <v>0.417</v>
       </c>
       <c r="H7">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2188,25 +2286,25 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8">
-        <v>126.94</v>
+        <v>145.62</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>117.43</v>
+        <v>110.2</v>
       </c>
       <c r="G8">
-        <v>0.538</v>
+        <v>0.542</v>
       </c>
       <c r="H8">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2214,28 +2312,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>121.24</v>
+        <v>130.01</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>113.18</v>
+        <v>111.64</v>
       </c>
       <c r="G9">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="H9">
         <v>-0.8</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2243,28 +2341,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10">
-        <v>151.37</v>
+        <v>115.61</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10">
-        <v>110.96</v>
+        <v>111.53</v>
       </c>
       <c r="G10">
-        <v>0.385</v>
+        <v>0.5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2272,28 +2370,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>136.73</v>
+        <v>126.28</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>109.97</v>
+        <v>108.79</v>
       </c>
       <c r="G11">
-        <v>0.462</v>
+        <v>0.417</v>
       </c>
       <c r="H11">
-        <v>-1.1</v>
+        <v>-1.8</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2308,321 +2406,321 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>151.37</v>
+        <v>145.625</v>
       </c>
       <c r="E2">
-        <v>151.37</v>
+        <v>291.25</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>136.73</v>
+        <v>130.015</v>
       </c>
       <c r="E3">
-        <v>136.73</v>
+        <v>260.03</v>
       </c>
       <c r="F3">
-        <v>99</v>
+        <v>99.8</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>126.24</v>
+        <v>120.72</v>
       </c>
       <c r="E4">
-        <v>126.24</v>
+        <v>241.44</v>
       </c>
       <c r="F4">
-        <v>90.60000000000001</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>126.94</v>
+        <v>126.285</v>
       </c>
       <c r="E5">
-        <v>126.94</v>
+        <v>252.57</v>
       </c>
       <c r="F5">
-        <v>90.3</v>
+        <v>94.3</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>125.15</v>
+        <v>115.605</v>
       </c>
       <c r="E6">
-        <v>125.15</v>
+        <v>231.21</v>
       </c>
       <c r="F6">
-        <v>77.2</v>
+        <v>69.39999999999999</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>121.24</v>
+        <v>113.255</v>
       </c>
       <c r="E7">
-        <v>121.24</v>
+        <v>226.51</v>
       </c>
       <c r="F7">
-        <v>67.40000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="G7">
-        <v>0.1</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>119.32</v>
+        <v>101.95</v>
       </c>
       <c r="E8">
-        <v>119.32</v>
+        <v>203.9</v>
       </c>
       <c r="F8">
-        <v>57.99999999999999</v>
+        <v>51.9</v>
       </c>
       <c r="G8">
-        <v>0.1</v>
+        <v>3.9</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>108.34</v>
+        <v>98.895</v>
       </c>
       <c r="E9">
-        <v>108.34</v>
+        <v>197.79</v>
       </c>
       <c r="F9">
-        <v>16.7</v>
+        <v>21.5</v>
       </c>
       <c r="G9">
-        <v>1.4</v>
+        <v>14.2</v>
       </c>
       <c r="H9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>74.98</v>
+        <v>90.45</v>
       </c>
       <c r="E10">
-        <v>74.98</v>
+        <v>180.9</v>
       </c>
       <c r="F10">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
       <c r="G10">
-        <v>27.5</v>
+        <v>24.4</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
-        <v>74.45</v>
+        <v>84.035</v>
       </c>
       <c r="E11">
-        <v>74.45</v>
+        <v>168.07</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>70.89999999999999</v>
+        <v>52.7</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2637,19 +2735,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2657,19 +2755,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
         <v>46</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2677,19 +2775,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2697,19 +2795,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
       <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2717,19 +2815,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
-      <c r="F5">
-        <v>0</v>
+      <c r="F5" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2737,19 +2835,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2757,19 +2855,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2777,19 +2875,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2797,19 +2895,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2817,19 +2915,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2837,19 +2935,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D11">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2859,125 +2957,158 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>92</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
         <v>8</v>
       </c>
-      <c r="B4">
+      <c r="D4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
         <v>4</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
       <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>-5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>-11</v>
+      </c>
+      <c r="C9">
+        <v>-8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>-1</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
+      <c r="C10">
+        <v>-12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>-8</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11">
-        <v>-11</v>
-      </c>
       <c r="C11">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Game of Yards! 2026.xlsx
+++ b/data/leagues/Game of Yards! 2026.xlsx
@@ -208,34 +208,34 @@
     <t>0-2</t>
   </si>
   <si>
-    <t>11.2-2.7-0.1</t>
-  </si>
-  <si>
-    <t>10.4-3.4-0.1</t>
-  </si>
-  <si>
-    <t>8.9-5.0-0.1</t>
-  </si>
-  <si>
-    <t>8.4-5.6-0.1</t>
-  </si>
-  <si>
-    <t>6.4-7.5-0.1</t>
-  </si>
-  <si>
-    <t>5.7-8.1-0.1</t>
-  </si>
-  <si>
-    <t>6.1-7.8-0.1</t>
+    <t>11.1-2.8-0.1</t>
+  </si>
+  <si>
+    <t>10.5-3.4-0.1</t>
+  </si>
+  <si>
+    <t>8.8-5.1-0.1</t>
+  </si>
+  <si>
+    <t>8.3-5.6-0.1</t>
+  </si>
+  <si>
+    <t>6.5-7.4-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.0-0.1</t>
+  </si>
+  <si>
+    <t>5.9-8.0-0.1</t>
   </si>
   <si>
     <t>4.7-9.2-0.1</t>
   </si>
   <si>
-    <t>4.2-9.7-0.1</t>
-  </si>
-  <si>
-    <t>3.5-10.5-0.1</t>
+    <t>4.3-9.6-0.1</t>
+  </si>
+  <si>
+    <t>3.5-10.4-0.1</t>
   </si>
   <si>
     <t>11-3</t>
@@ -244,7 +244,7 @@
     <t>9-5</t>
   </si>
   <si>
-    <t>7-7</t>
+    <t>8-6</t>
   </si>
   <si>
     <t>6-8</t>
@@ -1532,25 +1532,25 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>62.9</v>
+        <v>61.9</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="D2">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
       <c r="E2">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="F2">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1570,25 +1570,25 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>25.8</v>
+        <v>27.6</v>
       </c>
       <c r="C3">
-        <v>42.7</v>
+        <v>43.7</v>
       </c>
       <c r="D3">
-        <v>21.5</v>
+        <v>19.7</v>
       </c>
       <c r="E3">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="F3">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G3">
         <v>0.3</v>
       </c>
       <c r="H3">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1608,37 +1608,37 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="C4">
-        <v>16</v>
+        <v>16.9</v>
       </c>
       <c r="D4">
-        <v>31.2</v>
+        <v>29.8</v>
       </c>
       <c r="E4">
-        <v>24.4</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>13.3</v>
+        <v>10.7</v>
       </c>
       <c r="G4">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="H4">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>96.90000000000001</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1646,37 +1646,37 @@
         <v>0</v>
       </c>
       <c r="B5">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="C5">
-        <v>14.1</v>
+        <v>12.7</v>
       </c>
       <c r="D5">
-        <v>26.6</v>
+        <v>27.7</v>
       </c>
       <c r="E5">
-        <v>28.6</v>
+        <v>26.4</v>
       </c>
       <c r="F5">
-        <v>12.9</v>
+        <v>14.2</v>
       </c>
       <c r="G5">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="H5">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="I5">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J5">
         <v>0.8</v>
       </c>
       <c r="K5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L5">
-        <v>94.3</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1684,37 +1684,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C6">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="D6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="E6">
-        <v>15.7</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>25.8</v>
+        <v>27.9</v>
       </c>
       <c r="G6">
-        <v>21.7</v>
+        <v>22.2</v>
       </c>
       <c r="H6">
-        <v>16.1</v>
+        <v>14.3</v>
       </c>
       <c r="I6">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="J6">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="K6">
         <v>1.4</v>
       </c>
       <c r="L6">
-        <v>69.40000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1725,34 +1725,34 @@
         <v>0.1</v>
       </c>
       <c r="C7">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D7">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="E7">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="F7">
-        <v>15.6</v>
+        <v>21</v>
       </c>
       <c r="G7">
-        <v>24.1</v>
+        <v>22.3</v>
       </c>
       <c r="H7">
-        <v>20.3</v>
+        <v>21.1</v>
       </c>
       <c r="I7">
         <v>14.9</v>
       </c>
       <c r="J7">
-        <v>9.699999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="K7">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="L7">
-        <v>51.9</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1760,37 +1760,37 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D8">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="E8">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="F8">
-        <v>19.6</v>
+        <v>14.4</v>
       </c>
       <c r="G8">
         <v>21.1</v>
       </c>
       <c r="H8">
-        <v>20.4</v>
+        <v>22.4</v>
       </c>
       <c r="I8">
-        <v>15.2</v>
+        <v>14.7</v>
       </c>
       <c r="J8">
-        <v>8.6</v>
+        <v>11.4</v>
       </c>
       <c r="K8">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
-        <v>51.9</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1801,34 +1801,34 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="G9">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="H9">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="I9">
-        <v>25.2</v>
+        <v>27.4</v>
       </c>
       <c r="J9">
-        <v>20.3</v>
+        <v>21.4</v>
       </c>
       <c r="K9">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="L9">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1839,34 +1839,34 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D10">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E10">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G10">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="H10">
-        <v>13.4</v>
+        <v>12.8</v>
       </c>
       <c r="I10">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="J10">
-        <v>30.3</v>
+        <v>31.4</v>
       </c>
       <c r="K10">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="L10">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1883,28 +1883,28 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F11">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="G11">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="H11">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="I11">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="J11">
-        <v>25.7</v>
+        <v>22.7</v>
       </c>
       <c r="K11">
-        <v>52.7</v>
+        <v>55</v>
       </c>
       <c r="L11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1930,10 +1930,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>91.7</v>
+        <v>90.5</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1944,16 +1944,16 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>90.7</v>
+        <v>92.80000000000001</v>
       </c>
       <c r="C3">
         <v>100</v>
       </c>
       <c r="D3">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1961,13 +1961,13 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>99</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C4">
-        <v>96.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D4">
-        <v>97.39999999999999</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1978,7 +1978,7 @@
         <v>99.8</v>
       </c>
       <c r="C5">
-        <v>91.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="D5">
         <v>93.8</v>
@@ -1989,13 +1989,13 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="C6">
-        <v>65.2</v>
+        <v>61.3</v>
       </c>
       <c r="D6">
-        <v>71.8</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2003,13 +2003,13 @@
         <v>2</v>
       </c>
       <c r="B7">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="C7">
-        <v>57.4</v>
+        <v>57.9</v>
       </c>
       <c r="D7">
-        <v>53.2</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2017,13 +2017,13 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>66</v>
+        <v>63.6</v>
       </c>
       <c r="C8">
-        <v>53.2</v>
+        <v>52.8</v>
       </c>
       <c r="D8">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2031,13 +2031,13 @@
         <v>3</v>
       </c>
       <c r="B9">
-        <v>59.4</v>
+        <v>61.2</v>
       </c>
       <c r="C9">
-        <v>20.6</v>
+        <v>23.6</v>
       </c>
       <c r="D9">
-        <v>19.1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2045,13 +2045,13 @@
         <v>5</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C10">
-        <v>11.6</v>
+        <v>10.6</v>
       </c>
       <c r="D10">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2059,13 +2059,13 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C11">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="D11">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>
@@ -2450,7 +2450,7 @@
         <v>291.25</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2479,7 +2479,7 @@
         <v>260.03</v>
       </c>
       <c r="F3">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>241.44</v>
       </c>
       <c r="F4">
-        <v>96.89999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="G4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
         <v>63</v>
@@ -2537,16 +2537,16 @@
         <v>252.57</v>
       </c>
       <c r="F5">
-        <v>94.3</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="s">
         <v>64</v>
       </c>
       <c r="I5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2566,7 +2566,7 @@
         <v>231.21</v>
       </c>
       <c r="F6">
-        <v>69.39999999999999</v>
+        <v>72</v>
       </c>
       <c r="G6">
         <v>1.4</v>
@@ -2575,7 +2575,7 @@
         <v>65</v>
       </c>
       <c r="I6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2595,10 +2595,10 @@
         <v>226.51</v>
       </c>
       <c r="F7">
-        <v>51.9</v>
+        <v>54.8</v>
       </c>
       <c r="G7">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="H7" t="s">
         <v>66</v>
@@ -2624,10 +2624,10 @@
         <v>203.9</v>
       </c>
       <c r="F8">
-        <v>51.9</v>
+        <v>47.7</v>
       </c>
       <c r="G8">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H8" t="s">
         <v>67</v>
@@ -2653,10 +2653,10 @@
         <v>197.79</v>
       </c>
       <c r="F9">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="G9">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="H9" t="s">
         <v>68</v>
@@ -2682,10 +2682,10 @@
         <v>180.9</v>
       </c>
       <c r="F10">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="G10">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="H10" t="s">
         <v>69</v>
@@ -2711,10 +2711,10 @@
         <v>168.07</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>52.7</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="H11" t="s">
         <v>70</v>

--- a/data/leagues/Game of Yards! 2026.xlsx
+++ b/data/leagues/Game of Yards! 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="103">
   <si>
     <t>Groot-o-Matic</t>
   </si>
@@ -55,13 +55,16 @@
     <t>Team HebAchi</t>
   </si>
   <si>
-    <t>1-1-0</t>
-  </si>
-  <si>
-    <t>0-2-0</t>
-  </si>
-  <si>
-    <t>2-0-0</t>
+    <t>2-1-0</t>
+  </si>
+  <si>
+    <t>1-2-0</t>
+  </si>
+  <si>
+    <t>0-3-0</t>
+  </si>
+  <si>
+    <t>3-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -124,6 +127,9 @@
     <t>Week_3</t>
   </si>
   <si>
+    <t>Week_4</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -145,36 +151,36 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Vidhi Sethia</t>
+  </si>
+  <si>
+    <t>Shihab Chowdhury</t>
+  </si>
+  <si>
+    <t>Kabir Manocha</t>
+  </si>
+  <si>
+    <t>Utkarsh Gupta</t>
+  </si>
+  <si>
+    <t>Saurin Sethia</t>
+  </si>
+  <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
-    <t>Shihab Chowdhury</t>
+    <t>Achira Amur</t>
   </si>
   <si>
     <t>Hayat Khan</t>
   </si>
   <si>
-    <t>Kabir Manocha</t>
-  </si>
-  <si>
-    <t>Vidhi Sethia</t>
-  </si>
-  <si>
     <t>Pawan Bhambhwani</t>
   </si>
   <si>
-    <t>Achira Amur</t>
-  </si>
-  <si>
-    <t>Saurin Sethia</t>
-  </si>
-  <si>
     <t>Harshit Aggarwal</t>
   </si>
   <si>
-    <t>Utkarsh Gupta</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -199,63 +205,63 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>11.1-2.8-0.1</t>
-  </si>
-  <si>
-    <t>10.5-3.4-0.1</t>
-  </si>
-  <si>
-    <t>8.8-5.1-0.1</t>
-  </si>
-  <si>
-    <t>8.3-5.6-0.1</t>
-  </si>
-  <si>
-    <t>6.5-7.4-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.0-0.1</t>
-  </si>
-  <si>
-    <t>5.9-8.0-0.1</t>
-  </si>
-  <si>
-    <t>4.7-9.2-0.1</t>
-  </si>
-  <si>
-    <t>4.3-9.6-0.1</t>
-  </si>
-  <si>
-    <t>3.5-10.4-0.1</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>11.6-2.4-0.1</t>
+  </si>
+  <si>
+    <t>11.1-2.9-0.1</t>
+  </si>
+  <si>
+    <t>7.8-6.1-0.1</t>
+  </si>
+  <si>
+    <t>7.4-6.5-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.1-0.1</t>
+  </si>
+  <si>
+    <t>5.5-8.4-0.1</t>
+  </si>
+  <si>
+    <t>5.4-8.5-0.1</t>
+  </si>
+  <si>
+    <t>3.2-10.7-0.1</t>
+  </si>
+  <si>
+    <t>2.9-11.0-0.1</t>
+  </si>
+  <si>
+    <t>12-2</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
-    <t>9-5</t>
-  </si>
-  <si>
     <t>8-6</t>
   </si>
   <si>
+    <t>7-7</t>
+  </si>
+  <si>
     <t>6-8</t>
   </si>
   <si>
     <t>5-9</t>
   </si>
   <si>
-    <t>4-10</t>
-  </si>
-  <si>
     <t>3-11</t>
   </si>
   <si>
@@ -268,40 +274,43 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑5</t>
-  </si>
-  <si>
-    <t>↑9</t>
+    <t>↑6</t>
   </si>
   <si>
     <t>↑2</t>
   </si>
   <si>
-    <t>↑6</t>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↓5</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↓9</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↓11</t>
-  </si>
-  <si>
-    <t>↓4</t>
+    <t>↓8</t>
   </si>
   <si>
     <t>Week 1</t>
   </si>
   <si>
     <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
   </si>
   <si>
     <t>Week</t>
@@ -723,31 +732,31 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -758,31 +767,31 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -793,7 +802,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -802,22 +811,22 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -825,34 +834,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -863,19 +872,19 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -884,10 +893,10 @@
         <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -898,7 +907,7 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -933,31 +942,31 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" t="s">
         <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -968,31 +977,31 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H9" t="s">
         <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1003,7 +1012,7 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -1015,7 +1024,7 @@
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" t="s">
         <v>10</v>
@@ -1027,7 +1036,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1035,34 +1044,34 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" t="s">
         <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1072,30 +1081,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1103,25 +1112,77 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
       <c r="E2">
-        <v>-8</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>-8</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>-1</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1136,13 +1197,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1153,10 +1214,10 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1164,10 +1225,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1181,7 +1242,7 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1192,13 +1253,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1206,10 +1267,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -1220,13 +1281,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1234,13 +1295,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1248,13 +1309,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1262,13 +1323,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1279,10 +1340,10 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1297,16 +1358,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1314,16 +1375,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="D2">
-        <v>-0.2</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1331,16 +1392,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="D3">
-        <v>-0.3999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1348,16 +1409,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="D4">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1365,13 +1426,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="D5">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1382,16 +1443,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="D6">
-        <v>0.9</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1399,13 +1460,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="D7">
-        <v>0.9</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -1416,16 +1477,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="D8">
-        <v>-0.3</v>
+        <v>1.4</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1436,10 +1497,10 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="D9">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -1453,13 +1514,13 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1476,7 +1537,7 @@
         <v>0.3</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1491,63 +1552,63 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>61.9</v>
+        <v>53.2</v>
       </c>
       <c r="C2">
-        <v>24.1</v>
+        <v>42.3</v>
       </c>
       <c r="D2">
-        <v>9.6</v>
+        <v>3.5</v>
       </c>
       <c r="E2">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="F2">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="G2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1567,28 +1628,28 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>27.6</v>
+        <v>45.3</v>
       </c>
       <c r="C3">
-        <v>43.7</v>
+        <v>47.8</v>
       </c>
       <c r="D3">
-        <v>19.7</v>
+        <v>5.6</v>
       </c>
       <c r="E3">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="F3">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="G3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1600,278 +1661,278 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B4">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="C4">
-        <v>16.9</v>
+        <v>3.3</v>
       </c>
       <c r="D4">
-        <v>29.8</v>
+        <v>30.1</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>24.7</v>
       </c>
       <c r="F4">
-        <v>10.7</v>
+        <v>17.6</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>11.6</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J4">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
-        <v>96.5</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="C5">
-        <v>12.7</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>27.7</v>
+        <v>22.9</v>
       </c>
       <c r="E5">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="F5">
-        <v>14.2</v>
+        <v>20.5</v>
       </c>
       <c r="G5">
-        <v>7.5</v>
+        <v>12.8</v>
       </c>
       <c r="H5">
-        <v>3.9</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K5">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L5">
-        <v>93.59999999999999</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C6">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="D6">
-        <v>5.5</v>
+        <v>21.8</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>19.6</v>
       </c>
       <c r="F6">
-        <v>27.9</v>
+        <v>20.9</v>
       </c>
       <c r="G6">
-        <v>22.2</v>
+        <v>17.8</v>
       </c>
       <c r="H6">
-        <v>14.3</v>
+        <v>10.2</v>
       </c>
       <c r="I6">
-        <v>7.1</v>
+        <v>5.6</v>
       </c>
       <c r="J6">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="K6">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>72</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="D7">
-        <v>2.7</v>
+        <v>9.5</v>
       </c>
       <c r="E7">
-        <v>8.5</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>19.7</v>
       </c>
       <c r="G7">
-        <v>22.3</v>
+        <v>23.6</v>
       </c>
       <c r="H7">
-        <v>21.1</v>
+        <v>17</v>
       </c>
       <c r="I7">
-        <v>14.9</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>6.9</v>
+        <v>2.1</v>
       </c>
       <c r="K7">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="L7">
-        <v>54.8</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D8">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="E8">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="F8">
-        <v>14.4</v>
+        <v>10.4</v>
       </c>
       <c r="G8">
-        <v>21.1</v>
+        <v>16.2</v>
       </c>
       <c r="H8">
-        <v>22.4</v>
+        <v>24.6</v>
       </c>
       <c r="I8">
-        <v>14.7</v>
+        <v>28.4</v>
       </c>
       <c r="J8">
-        <v>11.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="L8">
-        <v>47.7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D9">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="E9">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="F9">
-        <v>5.9</v>
+        <v>9.5</v>
       </c>
       <c r="G9">
+        <v>16</v>
+      </c>
+      <c r="H9">
+        <v>25.3</v>
+      </c>
+      <c r="I9">
+        <v>26.8</v>
+      </c>
+      <c r="J9">
         <v>11.1</v>
       </c>
-      <c r="H9">
-        <v>16.7</v>
-      </c>
-      <c r="I9">
-        <v>27.4</v>
-      </c>
-      <c r="J9">
-        <v>21.4</v>
-      </c>
       <c r="K9">
-        <v>13.9</v>
+        <v>2</v>
       </c>
       <c r="L9">
-        <v>20.6</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="G10">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="H10">
-        <v>12.8</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>21.5</v>
+        <v>10.5</v>
       </c>
       <c r="J10">
-        <v>31.4</v>
+        <v>37.6</v>
       </c>
       <c r="K10">
-        <v>23.4</v>
+        <v>47.4</v>
       </c>
       <c r="L10">
-        <v>10.9</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1883,28 +1944,28 @@
         <v>0</v>
       </c>
       <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>0.2</v>
       </c>
-      <c r="F11">
-        <v>0.7</v>
-      </c>
       <c r="G11">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="H11">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="I11">
-        <v>11.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11">
-        <v>22.7</v>
+        <v>37.1</v>
       </c>
       <c r="K11">
-        <v>55</v>
+        <v>48.8</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -1914,158 +1975,191 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>90.5</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="D2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>92.80000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="C3">
         <v>100</v>
       </c>
       <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>98.5</v>
+      </c>
+      <c r="D4">
+        <v>91</v>
+      </c>
+      <c r="E4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>68.60000000000001</v>
+      </c>
+      <c r="C5">
+        <v>42.2</v>
+      </c>
+      <c r="D5">
+        <v>85.8</v>
+      </c>
+      <c r="E5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>2.9</v>
+      </c>
+      <c r="D6">
+        <v>79.60000000000001</v>
+      </c>
+      <c r="E6">
+        <v>80.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
         <v>99.7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="C4">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="D4">
-        <v>95.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>99.8</v>
-      </c>
-      <c r="C5">
-        <v>94</v>
-      </c>
-      <c r="D5">
-        <v>93.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="C7">
+        <v>99.3</v>
+      </c>
+      <c r="D7">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="E7">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>78.3</v>
+      </c>
+      <c r="C8">
+        <v>69.39999999999999</v>
+      </c>
+      <c r="D8">
+        <v>38</v>
+      </c>
+      <c r="E8">
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>13.3</v>
-      </c>
-      <c r="C6">
-        <v>61.3</v>
-      </c>
-      <c r="D6">
-        <v>69.59999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>78.2</v>
-      </c>
-      <c r="C7">
-        <v>57.9</v>
-      </c>
-      <c r="D7">
-        <v>55.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>63.6</v>
-      </c>
-      <c r="C8">
-        <v>52.8</v>
-      </c>
-      <c r="D8">
-        <v>50.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="B9">
+        <v>9.4</v>
+      </c>
+      <c r="C9">
+        <v>72.7</v>
+      </c>
+      <c r="D9">
+        <v>38.3</v>
+      </c>
+      <c r="E9">
+        <v>35.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>0.4</v>
+      </c>
+      <c r="C10">
+        <v>1.5</v>
+      </c>
+      <c r="D10">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="E10">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B9">
-        <v>61.2</v>
-      </c>
-      <c r="C9">
-        <v>23.6</v>
-      </c>
-      <c r="D9">
-        <v>21.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <v>0.1</v>
-      </c>
-      <c r="C10">
-        <v>10.6</v>
-      </c>
-      <c r="D10">
-        <v>10.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="B11">
+        <v>55.7</v>
+      </c>
+      <c r="C11">
+        <v>13.8</v>
+      </c>
+      <c r="D11">
         <v>1</v>
       </c>
-      <c r="B11">
-        <v>0.6</v>
-      </c>
-      <c r="C11">
-        <v>2.2</v>
-      </c>
-      <c r="D11">
-        <v>3.6</v>
+      <c r="E11">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -2080,28 +2174,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2109,28 +2203,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>90.45</v>
+        <v>108.15</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>119.08</v>
+        <v>114.87</v>
       </c>
       <c r="G2">
-        <v>0.583</v>
+        <v>0.515</v>
       </c>
       <c r="H2">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2141,25 +2235,25 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>98.89</v>
+        <v>86.13</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>112.82</v>
+        <v>110.93</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="H3">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2167,28 +2261,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4">
+        <v>106.82</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>114.33</v>
+      </c>
+      <c r="G4">
+        <v>0.576</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4">
-        <v>84.03</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>114.47</v>
-      </c>
-      <c r="G4">
-        <v>0.5</v>
-      </c>
-      <c r="H4">
-        <v>0.4</v>
-      </c>
       <c r="I4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2196,28 +2290,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>113.25</v>
+        <v>115.22</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>113.86</v>
+        <v>110.89</v>
       </c>
       <c r="G5">
-        <v>0.625</v>
+        <v>0.455</v>
       </c>
       <c r="H5">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2225,28 +2319,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6">
-        <v>120.72</v>
+        <v>139.27</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>112.95</v>
+        <v>111.6</v>
       </c>
       <c r="G6">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="H6">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2254,28 +2348,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>101.95</v>
+        <v>111.65</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>111.48</v>
+        <v>111.49</v>
       </c>
       <c r="G7">
-        <v>0.417</v>
+        <v>0.515</v>
       </c>
       <c r="H7">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2286,25 +2380,25 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8">
-        <v>145.62</v>
+        <v>145.33</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>110.2</v>
+        <v>110.62</v>
       </c>
       <c r="G8">
-        <v>0.542</v>
+        <v>0.545</v>
       </c>
       <c r="H8">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2312,28 +2406,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9">
-        <v>130.01</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>111.64</v>
+        <v>111.66</v>
       </c>
       <c r="G9">
-        <v>0.458</v>
+        <v>0.485</v>
       </c>
       <c r="H9">
         <v>-0.8</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2341,28 +2435,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10">
-        <v>115.61</v>
+        <v>110.43</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>111.53</v>
+        <v>108.55</v>
       </c>
       <c r="G10">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="H10">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2370,28 +2464,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11">
-        <v>126.28</v>
+        <v>108.71</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>108.79</v>
+        <v>109.76</v>
       </c>
       <c r="G11">
-        <v>0.417</v>
+        <v>0.515</v>
       </c>
       <c r="H11">
-        <v>-1.8</v>
+        <v>-2.3</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2406,48 +2500,48 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>145.625</v>
+        <v>139.2666666666667</v>
       </c>
       <c r="E2">
-        <v>291.25</v>
+        <v>417.8</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2456,271 +2550,271 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>130.015</v>
+        <v>145.33</v>
       </c>
       <c r="E3">
-        <v>260.03</v>
+        <v>435.99</v>
       </c>
       <c r="F3">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>120.72</v>
+        <v>115.2233333333333</v>
       </c>
       <c r="E4">
-        <v>241.44</v>
+        <v>345.67</v>
       </c>
       <c r="F4">
-        <v>96.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>126.285</v>
+        <v>110.43</v>
       </c>
       <c r="E5">
-        <v>252.57</v>
+        <v>331.29</v>
       </c>
       <c r="F5">
-        <v>93.60000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="G5">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D6">
-        <v>115.605</v>
+        <v>111.6466666666667</v>
       </c>
       <c r="E6">
-        <v>231.21</v>
+        <v>334.94</v>
       </c>
       <c r="F6">
-        <v>72</v>
+        <v>82.8</v>
       </c>
       <c r="G6">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D7">
-        <v>113.255</v>
+        <v>108.15</v>
       </c>
       <c r="E7">
-        <v>226.51</v>
+        <v>324.45</v>
       </c>
       <c r="F7">
-        <v>54.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8">
-        <v>101.95</v>
+        <v>106.82</v>
       </c>
       <c r="E8">
-        <v>203.9</v>
+        <v>320.46</v>
       </c>
       <c r="F8">
-        <v>47.7</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>98.895</v>
+        <v>108.71</v>
       </c>
       <c r="E9">
-        <v>197.79</v>
+        <v>326.13</v>
       </c>
       <c r="F9">
-        <v>20.6</v>
+        <v>34.8</v>
       </c>
       <c r="G9">
-        <v>13.9</v>
+        <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10">
-        <v>90.45</v>
+        <v>82.99666666666667</v>
       </c>
       <c r="E10">
-        <v>180.9</v>
+        <v>248.99</v>
       </c>
       <c r="F10">
-        <v>10.9</v>
+        <v>1.5</v>
       </c>
       <c r="G10">
-        <v>23.4</v>
+        <v>47.4</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>84.035</v>
+        <v>86.13333333333333</v>
       </c>
       <c r="E11">
-        <v>168.07</v>
+        <v>258.4</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="G11">
-        <v>55.00000000000001</v>
+        <v>48.8</v>
       </c>
       <c r="H11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2735,19 +2829,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2758,16 +2852,16 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2778,16 +2872,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2795,19 +2889,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2815,19 +2909,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2838,16 +2932,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2855,19 +2949,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2878,16 +2972,16 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2895,19 +2989,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2915,10 +3009,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D10">
         <v>-12</v>
@@ -2927,7 +3021,7 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2935,19 +3029,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11">
-        <v>-12</v>
+        <v>-20</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2957,21 +3051,24 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>95</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -2981,11 +3078,14 @@
       <c r="C2">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -2995,39 +3095,48 @@
       <c r="C3">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>6</v>
       </c>
-      <c r="C4">
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -3037,25 +3146,31 @@
       <c r="C6">
         <v>2</v>
       </c>
-      <c r="D6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>-8</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -3065,50 +3180,62 @@
       <c r="C8">
         <v>-5</v>
       </c>
-      <c r="D8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="D8">
+        <v>-1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B9">
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>-4</v>
+      </c>
+      <c r="E9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10">
         <v>-8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>-1</v>
       </c>
       <c r="C10">
         <v>-12</v>
       </c>
-      <c r="D10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="D10">
+        <v>-12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="C11">
         <v>-12</v>
       </c>
-      <c r="D11" t="s">
-        <v>90</v>
+      <c r="D11">
+        <v>-20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Game of Yards! 2026.xlsx
+++ b/data/leagues/Game of Yards! 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="105">
   <si>
     <t>Groot-o-Matic</t>
   </si>
@@ -55,16 +55,19 @@
     <t>Team HebAchi</t>
   </si>
   <si>
-    <t>2-1-0</t>
-  </si>
-  <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>0-3-0</t>
-  </si>
-  <si>
-    <t>3-0-0</t>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>4-0-0</t>
+  </si>
+  <si>
+    <t>0-4-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -130,6 +133,9 @@
     <t>Week_4</t>
   </si>
   <si>
+    <t>Week_5</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -154,33 +160,33 @@
     <t>Vidhi Sethia</t>
   </si>
   <si>
+    <t>Achira Amur</t>
+  </si>
+  <si>
+    <t>Pawan Bhambhwani</t>
+  </si>
+  <si>
     <t>Shihab Chowdhury</t>
   </si>
   <si>
+    <t>Utkarsh Gupta</t>
+  </si>
+  <si>
+    <t>Harshit Aggarwal</t>
+  </si>
+  <si>
+    <t>Hayat Khan</t>
+  </si>
+  <si>
     <t>Kabir Manocha</t>
   </si>
   <si>
-    <t>Utkarsh Gupta</t>
-  </si>
-  <si>
     <t>Saurin Sethia</t>
   </si>
   <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
-    <t>Achira Amur</t>
-  </si>
-  <si>
-    <t>Hayat Khan</t>
-  </si>
-  <si>
-    <t>Pawan Bhambhwani</t>
-  </si>
-  <si>
-    <t>Harshit Aggarwal</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -205,52 +211,58 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>11.6-2.4-0.1</t>
-  </si>
-  <si>
-    <t>11.1-2.9-0.1</t>
-  </si>
-  <si>
-    <t>7.8-6.1-0.1</t>
-  </si>
-  <si>
-    <t>7.4-6.5-0.1</t>
-  </si>
-  <si>
-    <t>6.7-7.1-0.1</t>
-  </si>
-  <si>
-    <t>5.5-8.4-0.1</t>
-  </si>
-  <si>
-    <t>5.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>3.2-10.7-0.1</t>
-  </si>
-  <si>
-    <t>2.9-11.0-0.1</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>11.8-2.1-0.1</t>
+  </si>
+  <si>
+    <t>10.0-3.9-0.1</t>
+  </si>
+  <si>
+    <t>8.4-5.5-0.1</t>
+  </si>
+  <si>
+    <t>6.8-7.1-0.1</t>
+  </si>
+  <si>
+    <t>6.6-7.3-0.1</t>
+  </si>
+  <si>
+    <t>6.2-7.7-0.1</t>
+  </si>
+  <si>
+    <t>5.5-8.3-0.1</t>
+  </si>
+  <si>
+    <t>5.0-8.9-0.1</t>
+  </si>
+  <si>
+    <t>5.1-8.8-0.1</t>
+  </si>
+  <si>
+    <t>4.1-9.8-0.1</t>
   </si>
   <si>
     <t>12-2</t>
   </si>
   <si>
-    <t>11-3</t>
-  </si>
-  <si>
-    <t>8-6</t>
+    <t>10-4</t>
+  </si>
+  <si>
+    <t>9-5</t>
   </si>
   <si>
     <t>7-7</t>
@@ -262,9 +274,6 @@
     <t>5-9</t>
   </si>
   <si>
-    <t>3-11</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -274,36 +283,30 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑6</t>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↓11</t>
   </si>
   <si>
     <t>↑2</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↓2</t>
-  </si>
-  <si>
-    <t>↑8</t>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↓8</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>↑4</t>
   </si>
   <si>
-    <t>↓5</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↓8</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -311,6 +314,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -770,16 +776,16 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
         <v>12</v>
@@ -805,25 +811,25 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K4" t="s">
         <v>11</v>
@@ -849,7 +855,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
         <v>12</v>
@@ -875,25 +881,25 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
         <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6" t="s">
         <v>11</v>
@@ -904,31 +910,31 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
         <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K7" t="s">
         <v>10</v>
@@ -951,10 +957,10 @@
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
@@ -974,31 +980,31 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" t="s">
         <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K9" t="s">
         <v>10</v>
@@ -1009,31 +1015,31 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" t="s">
         <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K10" t="s">
         <v>12</v>
@@ -1044,34 +1050,34 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1081,30 +1087,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1112,25 +1118,25 @@
         <v>0</v>
       </c>
       <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
       <c r="E2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="G2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1138,25 +1144,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>-12</v>
+      </c>
+      <c r="F3">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>-8</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
       <c r="G3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1167,22 +1173,100 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>16</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>-8</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D6" t="s">
         <v>4</v>
       </c>
-      <c r="E4">
+      <c r="E6">
         <v>-1</v>
       </c>
-      <c r="F4">
+      <c r="F6">
         <v>7</v>
       </c>
-      <c r="G4">
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H6" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>-12</v>
+      </c>
+      <c r="F7">
+        <v>-4</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1197,13 +1281,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1214,10 +1298,10 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1225,13 +1309,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1239,10 +1323,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1256,10 +1340,10 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1267,13 +1351,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1281,13 +1365,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1295,13 +1379,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1309,13 +1393,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1326,7 +1410,7 @@
         <v>3</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1340,7 +1424,7 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1358,16 +1442,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1378,10 +1462,10 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="D2">
-        <v>-0.3999999999999999</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -1392,13 +1476,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="D3">
-        <v>0.5</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1409,16 +1493,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="D4">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1429,10 +1513,10 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="D5">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1446,13 +1530,13 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="D6">
-        <v>-0.3999999999999999</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1463,13 +1547,13 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="D7">
-        <v>0.3999999999999999</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1480,13 +1564,13 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="D8">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1497,13 +1581,13 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="D9">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1514,10 +1598,10 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D10">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -1531,10 +1615,10 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="D11">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -1552,40 +1636,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1593,19 +1677,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>53.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="C2">
-        <v>42.3</v>
+        <v>17.7</v>
       </c>
       <c r="D2">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="E2">
         <v>0.7</v>
       </c>
       <c r="F2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1628,28 +1712,28 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B3">
-        <v>45.3</v>
+        <v>18</v>
       </c>
       <c r="C3">
-        <v>47.8</v>
+        <v>58.2</v>
       </c>
       <c r="D3">
-        <v>5.6</v>
+        <v>17.1</v>
       </c>
       <c r="E3">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="F3">
+        <v>1.4</v>
+      </c>
+      <c r="G3">
         <v>0.5</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1661,83 +1745,83 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>100</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>17.8</v>
+      </c>
+      <c r="D4">
+        <v>47.5</v>
+      </c>
+      <c r="E4">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>6.3</v>
+      </c>
+      <c r="G4">
+        <v>3.9</v>
+      </c>
+      <c r="H4">
+        <v>2.6</v>
+      </c>
+      <c r="I4">
+        <v>0.8</v>
+      </c>
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="B4">
-        <v>0.6</v>
-      </c>
-      <c r="C4">
-        <v>3.3</v>
-      </c>
-      <c r="D4">
-        <v>30.1</v>
-      </c>
-      <c r="E4">
-        <v>24.7</v>
-      </c>
-      <c r="F4">
-        <v>17.6</v>
-      </c>
-      <c r="G4">
-        <v>11.6</v>
-      </c>
-      <c r="H4">
-        <v>7.6</v>
-      </c>
-      <c r="I4">
-        <v>3.9</v>
-      </c>
-      <c r="J4">
-        <v>0.5</v>
       </c>
       <c r="K4">
         <v>0.1</v>
       </c>
       <c r="L4">
-        <v>87.90000000000001</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D5">
-        <v>22.9</v>
+        <v>10.6</v>
       </c>
       <c r="E5">
-        <v>26.3</v>
+        <v>19.6</v>
       </c>
       <c r="F5">
         <v>20.5</v>
       </c>
       <c r="G5">
-        <v>12.8</v>
+        <v>15.7</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>11.8</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>10.6</v>
       </c>
       <c r="J5">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="K5">
-        <v>0.1</v>
+        <v>3.2</v>
       </c>
       <c r="L5">
-        <v>86.3</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1748,72 +1832,72 @@
         <v>0.1</v>
       </c>
       <c r="C6">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="D6">
-        <v>21.8</v>
+        <v>7.8</v>
       </c>
       <c r="E6">
-        <v>19.6</v>
+        <v>22.1</v>
       </c>
       <c r="F6">
-        <v>20.9</v>
+        <v>20.2</v>
       </c>
       <c r="G6">
-        <v>17.8</v>
+        <v>15.5</v>
       </c>
       <c r="H6">
-        <v>10.2</v>
+        <v>12.2</v>
       </c>
       <c r="I6">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>1.4</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="L6">
-        <v>82.8</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D7">
-        <v>9.5</v>
+        <v>7.6</v>
       </c>
       <c r="E7">
         <v>16</v>
       </c>
       <c r="F7">
-        <v>19.7</v>
+        <v>16.9</v>
       </c>
       <c r="G7">
-        <v>23.6</v>
+        <v>17.2</v>
       </c>
       <c r="H7">
-        <v>17</v>
+        <v>14.7</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>12.8</v>
       </c>
       <c r="J7">
-        <v>2.1</v>
+        <v>8.9</v>
       </c>
       <c r="K7">
-        <v>0.3</v>
+        <v>4.7</v>
       </c>
       <c r="L7">
-        <v>69.59999999999999</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1821,42 +1905,42 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C8">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D8">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="E8">
-        <v>6.1</v>
+        <v>10.4</v>
       </c>
       <c r="F8">
-        <v>10.4</v>
+        <v>14.3</v>
       </c>
       <c r="G8">
-        <v>16.2</v>
+        <v>17.5</v>
       </c>
       <c r="H8">
-        <v>24.6</v>
+        <v>17.3</v>
       </c>
       <c r="I8">
-        <v>28.4</v>
+        <v>15.7</v>
       </c>
       <c r="J8">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="K8">
-        <v>1.3</v>
+        <v>9.1</v>
       </c>
       <c r="L8">
-        <v>36</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1865,31 +1949,31 @@
         <v>0.1</v>
       </c>
       <c r="D9">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="F9">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G9">
-        <v>16</v>
+        <v>10.9</v>
       </c>
       <c r="H9">
-        <v>25.3</v>
+        <v>14.8</v>
       </c>
       <c r="I9">
-        <v>26.8</v>
+        <v>18.9</v>
       </c>
       <c r="J9">
-        <v>11.1</v>
+        <v>19.8</v>
       </c>
       <c r="K9">
-        <v>2</v>
+        <v>21.6</v>
       </c>
       <c r="L9">
-        <v>34.8</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1900,72 +1984,72 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="F10">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="G10">
-        <v>1.1</v>
+        <v>10.7</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>13.7</v>
       </c>
       <c r="I10">
-        <v>10.5</v>
+        <v>15.4</v>
       </c>
       <c r="J10">
-        <v>37.6</v>
+        <v>25.6</v>
       </c>
       <c r="K10">
-        <v>47.4</v>
+        <v>23.6</v>
       </c>
       <c r="L10">
-        <v>1.5</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="F11">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>0.9</v>
+        <v>8.1</v>
       </c>
       <c r="H11">
-        <v>3.2</v>
+        <v>12.6</v>
       </c>
       <c r="I11">
-        <v>9.800000000000001</v>
+        <v>15.8</v>
       </c>
       <c r="J11">
-        <v>37.1</v>
+        <v>21.7</v>
       </c>
       <c r="K11">
-        <v>48.8</v>
+        <v>34.5</v>
       </c>
       <c r="L11">
-        <v>1.1</v>
+        <v>15.4</v>
       </c>
     </row>
   </sheetData>
@@ -1975,32 +2059,35 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>94.19999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="C2">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -2008,59 +2095,71 @@
       <c r="E2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>98</v>
+      </c>
+      <c r="D3">
+        <v>91.7</v>
+      </c>
+      <c r="E3">
+        <v>99.3</v>
+      </c>
+      <c r="F3">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3">
-        <v>93.7</v>
-      </c>
-      <c r="C3">
+      <c r="B4">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="C4">
         <v>100</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E3">
+      <c r="E4">
+        <v>98.7</v>
+      </c>
+      <c r="F4">
+        <v>97.89999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4">
-        <v>100</v>
-      </c>
-      <c r="C4">
-        <v>98.5</v>
-      </c>
-      <c r="D4">
-        <v>91</v>
-      </c>
-      <c r="E4">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
+      <c r="C5">
+        <v>99.2</v>
+      </c>
+      <c r="D5">
         <v>68.60000000000001</v>
       </c>
-      <c r="C5">
-        <v>42.2</v>
-      </c>
-      <c r="D5">
-        <v>85.8</v>
-      </c>
       <c r="E5">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>65.5</v>
+      </c>
+      <c r="F5">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -2068,98 +2167,116 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D6">
-        <v>79.60000000000001</v>
+        <v>77</v>
       </c>
       <c r="E6">
-        <v>80.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>62.4</v>
+      </c>
+      <c r="F6">
+        <v>64.09999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>99.7</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>99.3</v>
+        <v>44.4</v>
       </c>
       <c r="D7">
-        <v>65.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="E7">
-        <v>69.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>63.4</v>
+      </c>
+      <c r="F7">
+        <v>58.59999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B8">
-        <v>78.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="C8">
-        <v>69.39999999999999</v>
+        <v>65</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>39.90000000000001</v>
       </c>
       <c r="E8">
-        <v>37.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>39.90000000000001</v>
+      </c>
+      <c r="F8">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9">
-        <v>9.4</v>
+        <v>58.9</v>
       </c>
       <c r="C9">
-        <v>72.7</v>
+        <v>14.8</v>
       </c>
       <c r="D9">
-        <v>38.3</v>
+        <v>1.3</v>
       </c>
       <c r="E9">
-        <v>35.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>27.9</v>
+      </c>
+      <c r="F9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B10">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="D10">
         <v>0.8999999999999999</v>
       </c>
       <c r="E10">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>21.4</v>
+      </c>
+      <c r="F10">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11">
-        <v>55.7</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>13.8</v>
+        <v>74.3</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>35.6</v>
       </c>
       <c r="E11">
-        <v>1.3</v>
+        <v>21.5</v>
+      </c>
+      <c r="F11">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2174,28 +2291,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2206,25 +2323,25 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>108.15</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>114.87</v>
+        <v>113.37</v>
       </c>
       <c r="G2">
-        <v>0.515</v>
+        <v>0.475</v>
       </c>
       <c r="H2">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2232,28 +2349,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>86.13</v>
+        <v>129.72</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>110.93</v>
+        <v>113.85</v>
       </c>
       <c r="G3">
-        <v>0.485</v>
+        <v>0.55</v>
       </c>
       <c r="H3">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2261,28 +2378,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>106.82</v>
+        <v>105.53</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4">
-        <v>114.33</v>
+        <v>113.2</v>
       </c>
       <c r="G4">
-        <v>0.576</v>
+        <v>0.475</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2290,28 +2407,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5">
-        <v>115.22</v>
+        <v>100.88</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>110.89</v>
+        <v>112.25</v>
       </c>
       <c r="G5">
-        <v>0.455</v>
+        <v>0.525</v>
       </c>
       <c r="H5">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2319,28 +2436,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>139.27</v>
+        <v>134.34</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>111.6</v>
+        <v>110.2</v>
       </c>
       <c r="G6">
-        <v>0.455</v>
+        <v>0.425</v>
       </c>
       <c r="H6">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2348,28 +2465,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>111.65</v>
+        <v>107.39</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F7">
-        <v>111.49</v>
+        <v>115.59</v>
       </c>
       <c r="G7">
-        <v>0.515</v>
+        <v>0.575</v>
       </c>
       <c r="H7">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2377,28 +2494,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>145.33</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>110.62</v>
+        <v>113.54</v>
       </c>
       <c r="G8">
-        <v>0.545</v>
+        <v>0.475</v>
       </c>
       <c r="H8">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2406,28 +2523,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>83</v>
+        <v>108.6</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>111.66</v>
+        <v>112.59</v>
       </c>
       <c r="G9">
-        <v>0.485</v>
+        <v>0.525</v>
       </c>
       <c r="H9">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2435,28 +2552,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10">
-        <v>110.43</v>
+        <v>139.3</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>108.55</v>
+        <v>111.94</v>
       </c>
       <c r="G10">
-        <v>0.455</v>
+        <v>0.45</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>-1.3</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2464,28 +2581,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11">
-        <v>108.71</v>
+        <v>106.78</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11">
-        <v>109.76</v>
+        <v>112.42</v>
       </c>
       <c r="G11">
-        <v>0.515</v>
+        <v>0.525</v>
       </c>
       <c r="H11">
-        <v>-2.3</v>
+        <v>-1.5</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2500,31 +2617,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2532,16 +2649,16 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>139.2666666666667</v>
+        <v>139.3025</v>
       </c>
       <c r="E2">
-        <v>417.8</v>
+        <v>557.2099999999999</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2550,97 +2667,97 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D3">
-        <v>145.33</v>
+        <v>134.345</v>
       </c>
       <c r="E3">
-        <v>435.99</v>
+        <v>537.38</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
-        <v>115.2233333333333</v>
+        <v>129.725</v>
       </c>
       <c r="E4">
-        <v>345.67</v>
+        <v>518.9</v>
       </c>
       <c r="F4">
-        <v>87.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="G4">
         <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D5">
-        <v>110.43</v>
+        <v>102.0025</v>
       </c>
       <c r="E5">
-        <v>331.29</v>
+        <v>408.01</v>
       </c>
       <c r="F5">
-        <v>86.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2648,57 +2765,57 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C6">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>111.6466666666667</v>
+        <v>106.7825</v>
       </c>
       <c r="E6">
-        <v>334.94</v>
+        <v>427.13</v>
       </c>
       <c r="F6">
-        <v>82.8</v>
+        <v>67.60000000000001</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C7">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>108.15</v>
+        <v>105.5275</v>
       </c>
       <c r="E7">
-        <v>324.45</v>
+        <v>422.11</v>
       </c>
       <c r="F7">
-        <v>69.59999999999999</v>
+        <v>58.9</v>
       </c>
       <c r="G7">
-        <v>0.3</v>
+        <v>4.7</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2706,57 +2823,57 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C8">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D8">
-        <v>106.82</v>
+        <v>108.5975</v>
       </c>
       <c r="E8">
-        <v>320.46</v>
+        <v>434.39</v>
       </c>
       <c r="F8">
-        <v>36</v>
+        <v>46.2</v>
       </c>
       <c r="G8">
-        <v>1.3</v>
+        <v>9.1</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D9">
-        <v>108.71</v>
+        <v>100.885</v>
       </c>
       <c r="E9">
-        <v>326.13</v>
+        <v>403.54</v>
       </c>
       <c r="F9">
-        <v>34.8</v>
+        <v>24.9</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>21.6</v>
       </c>
       <c r="H9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2764,57 +2881,57 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C10">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>82.99666666666667</v>
+        <v>94.39750000000001</v>
       </c>
       <c r="E10">
-        <v>248.99</v>
+        <v>377.59</v>
       </c>
       <c r="F10">
-        <v>1.5</v>
+        <v>21.7</v>
       </c>
       <c r="G10">
-        <v>47.4</v>
+        <v>23.6</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>86.13333333333333</v>
+        <v>107.39</v>
       </c>
       <c r="E11">
-        <v>258.4</v>
+        <v>429.56</v>
       </c>
       <c r="F11">
-        <v>1.1</v>
+        <v>15.4</v>
       </c>
       <c r="G11">
-        <v>48.8</v>
+        <v>34.5</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2829,19 +2946,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2849,19 +2966,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2869,19 +2986,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2889,19 +3006,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D4">
         <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2909,19 +3026,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
         <v>45</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2932,16 +3049,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2952,16 +3069,16 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2972,16 +3089,16 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2992,16 +3109,16 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3012,7 +3129,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10">
         <v>-12</v>
@@ -3021,7 +3138,7 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3032,16 +3149,16 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D11">
-        <v>-20</v>
+        <v>-16</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3051,92 +3168,107 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>97</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
+      <c r="B5">
         <v>5</v>
       </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-      <c r="D3">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>8</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -3149,11 +3281,14 @@
       <c r="D6">
         <v>0</v>
       </c>
-      <c r="E6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -3166,11 +3301,14 @@
       <c r="D7">
         <v>0</v>
       </c>
-      <c r="E7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -3183,11 +3321,14 @@
       <c r="D8">
         <v>-1</v>
       </c>
-      <c r="E8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="E8">
+        <v>-4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -3200,11 +3341,14 @@
       <c r="D9">
         <v>-4</v>
       </c>
-      <c r="E9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="E9">
+        <v>-12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
@@ -3217,11 +3361,14 @@
       <c r="D10">
         <v>-12</v>
       </c>
-      <c r="E10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="E10">
+        <v>-12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -3234,8 +3381,11 @@
       <c r="D11">
         <v>-20</v>
       </c>
-      <c r="E11" t="s">
-        <v>92</v>
+      <c r="E11">
+        <v>-16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Game of Yards! 2026.xlsx
+++ b/data/leagues/Game of Yards! 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="108">
   <si>
     <t>Groot-o-Matic</t>
   </si>
@@ -55,19 +55,22 @@
     <t>Team HebAchi</t>
   </si>
   <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
-    <t>4-0-0</t>
-  </si>
-  <si>
-    <t>0-4-0</t>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>4-1-0</t>
+  </si>
+  <si>
+    <t>0-5-0</t>
+  </si>
+  <si>
+    <t>1-4-0</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -136,6 +139,9 @@
     <t>Week_5</t>
   </si>
   <si>
+    <t>Week_6</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -157,36 +163,36 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Shihab Chowdhury</t>
+  </si>
+  <si>
+    <t>Hayat Khan</t>
+  </si>
+  <si>
     <t>Vidhi Sethia</t>
   </si>
   <si>
+    <t>Pawan Bhambhwani</t>
+  </si>
+  <si>
+    <t>Kabir Manocha</t>
+  </si>
+  <si>
+    <t>Utkarsh Gupta</t>
+  </si>
+  <si>
+    <t>Harshit Aggarwal</t>
+  </si>
+  <si>
+    <t>Prahlad Singh</t>
+  </si>
+  <si>
     <t>Achira Amur</t>
   </si>
   <si>
-    <t>Pawan Bhambhwani</t>
-  </si>
-  <si>
-    <t>Shihab Chowdhury</t>
-  </si>
-  <si>
-    <t>Utkarsh Gupta</t>
-  </si>
-  <si>
-    <t>Harshit Aggarwal</t>
-  </si>
-  <si>
-    <t>Hayat Khan</t>
-  </si>
-  <si>
-    <t>Kabir Manocha</t>
-  </si>
-  <si>
     <t>Saurin Sethia</t>
   </si>
   <si>
-    <t>Prahlad Singh</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -211,52 +217,49 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>11.8-2.1-0.1</t>
-  </si>
-  <si>
-    <t>10.0-3.9-0.1</t>
-  </si>
-  <si>
-    <t>8.4-5.5-0.1</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>6.6-7.3-0.1</t>
-  </si>
-  <si>
-    <t>6.2-7.7-0.1</t>
-  </si>
-  <si>
-    <t>5.5-8.3-0.1</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>10.6-3.4-0.1</t>
+  </si>
+  <si>
+    <t>9.6-4.4-0.1</t>
+  </si>
+  <si>
+    <t>8.6-5.3-0.1</t>
+  </si>
+  <si>
+    <t>7.2-6.7-0.1</t>
+  </si>
+  <si>
+    <t>7.3-6.6-0.1</t>
+  </si>
+  <si>
+    <t>6.9-7.1-0.1</t>
+  </si>
+  <si>
+    <t>5.7-8.2-0.1</t>
   </si>
   <si>
     <t>5.0-8.9-0.1</t>
   </si>
   <si>
-    <t>5.1-8.8-0.1</t>
-  </si>
-  <si>
-    <t>4.1-9.8-0.1</t>
-  </si>
-  <si>
-    <t>12-2</t>
+    <t>4.6-9.3-0.1</t>
+  </si>
+  <si>
+    <t>4.2-9.7-0.1</t>
+  </si>
+  <si>
+    <t>11-3</t>
   </si>
   <si>
     <t>10-4</t>
@@ -268,12 +271,15 @@
     <t>7-7</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>8-6</t>
   </si>
   <si>
     <t>5-9</t>
   </si>
   <si>
+    <t>4-10</t>
+  </si>
+  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -283,22 +289,22 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑2</t>
+  </si>
+  <si>
     <t>↑5</t>
   </si>
   <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↓11</t>
-  </si>
-  <si>
-    <t>↑2</t>
+    <t>↑6</t>
   </si>
   <si>
     <t>↓3</t>
   </si>
   <si>
-    <t>↓8</t>
+    <t>↓5</t>
+  </si>
+  <si>
+    <t>↓2</t>
   </si>
   <si>
     <t>0</t>
@@ -317,6 +323,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -744,7 +753,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -759,7 +768,7 @@
         <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
         <v>11</v>
@@ -776,28 +785,28 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
-      </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -811,25 +820,25 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" t="s">
-        <v>12</v>
       </c>
       <c r="K4" t="s">
         <v>11</v>
@@ -840,34 +849,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I5" t="s">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -875,7 +884,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -884,7 +893,7 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
@@ -893,16 +902,16 @@
         <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
         <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -910,34 +919,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="J7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" t="s">
         <v>12</v>
-      </c>
-      <c r="G7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K7" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -948,31 +957,31 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -980,34 +989,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" t="s">
         <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K9" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1015,34 +1024,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" t="s">
         <v>12</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" t="s">
-        <v>10</v>
-      </c>
       <c r="J10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1050,34 +1059,34 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1087,30 +1096,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1222,25 +1231,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1248,25 +1257,103 @@
         <v>5</v>
       </c>
       <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
       <c r="E7">
-        <v>-12</v>
+        <v>-1</v>
       </c>
       <c r="F7">
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>8</v>
       </c>
       <c r="H7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
         <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>-12</v>
+      </c>
+      <c r="F8">
+        <v>-4</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>-4</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>-18</v>
+      </c>
+      <c r="F10">
+        <v>-17</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1281,13 +1368,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1298,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -1312,10 +1399,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1326,10 +1413,10 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1337,13 +1424,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1351,13 +1438,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1365,13 +1452,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1379,13 +1466,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1393,13 +1480,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1407,13 +1494,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1421,13 +1508,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1442,16 +1529,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1462,13 +1549,13 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D2">
-        <v>-0.6000000000000001</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1476,13 +1563,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="D3">
-        <v>-0.2999999999999998</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1493,16 +1580,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1510,13 +1597,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="D5">
-        <v>-1.1</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1527,16 +1614,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="D6">
-        <v>-0.1000000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1544,16 +1631,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="D7">
-        <v>0.8999999999999999</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1564,10 +1651,10 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="D8">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
@@ -1578,16 +1665,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="D9">
-        <v>-0.5</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1595,13 +1682,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="D10">
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -1612,16 +1699,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="D11">
-        <v>0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1636,40 +1723,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1677,22 +1764,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>78.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="C2">
-        <v>17.7</v>
+        <v>32.1</v>
       </c>
       <c r="D2">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="F2">
+        <v>0.5</v>
+      </c>
+      <c r="G2">
         <v>0.2</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1712,31 +1799,31 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>31.8</v>
       </c>
       <c r="C3">
-        <v>58.2</v>
+        <v>35.4</v>
       </c>
       <c r="D3">
-        <v>17.1</v>
+        <v>20.6</v>
       </c>
       <c r="E3">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="F3">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="H3">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1745,83 +1832,83 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.7</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>10.5</v>
       </c>
       <c r="C4">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="D4">
-        <v>47.5</v>
+        <v>37.2</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
       <c r="G4">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="H4">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="I4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J4">
+        <v>0.3</v>
+      </c>
+      <c r="K4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0.1</v>
-      </c>
       <c r="L4">
-        <v>96.5</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="C5">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D5">
-        <v>10.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E5">
-        <v>19.6</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>20.5</v>
+        <v>24.2</v>
       </c>
       <c r="G5">
-        <v>15.7</v>
+        <v>18.6</v>
       </c>
       <c r="H5">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="I5">
-        <v>10.6</v>
+        <v>5.6</v>
       </c>
       <c r="J5">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="L5">
-        <v>69.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1829,151 +1916,151 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="C6">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="D6">
-        <v>7.8</v>
+        <v>13.4</v>
       </c>
       <c r="E6">
-        <v>22.1</v>
+        <v>21.2</v>
       </c>
       <c r="F6">
-        <v>20.2</v>
+        <v>22.4</v>
       </c>
       <c r="G6">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="H6">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="K6">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="L6">
-        <v>67.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C7">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="D7">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>19.3</v>
       </c>
       <c r="F7">
-        <v>16.9</v>
+        <v>18.2</v>
       </c>
       <c r="G7">
-        <v>17.2</v>
+        <v>21.1</v>
       </c>
       <c r="H7">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="I7">
-        <v>12.8</v>
+        <v>9.1</v>
       </c>
       <c r="J7">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="K7">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>58.9</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="D8">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="E8">
-        <v>10.4</v>
+        <v>6.2</v>
       </c>
       <c r="F8">
-        <v>14.3</v>
+        <v>11.7</v>
       </c>
       <c r="G8">
-        <v>17.5</v>
+        <v>15.6</v>
       </c>
       <c r="H8">
-        <v>17.3</v>
+        <v>20.2</v>
       </c>
       <c r="I8">
-        <v>15.7</v>
+        <v>20.1</v>
       </c>
       <c r="J8">
-        <v>11.7</v>
+        <v>14.1</v>
       </c>
       <c r="K8">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="L8">
-        <v>46.2</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="E9">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="F9">
-        <v>8.699999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="G9">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="H9">
-        <v>14.8</v>
+        <v>19</v>
       </c>
       <c r="I9">
-        <v>18.9</v>
+        <v>23.9</v>
       </c>
       <c r="J9">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="K9">
-        <v>21.6</v>
+        <v>14</v>
       </c>
       <c r="L9">
-        <v>24.9</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1984,72 +2071,72 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="E10">
+        <v>1.3</v>
+      </c>
+      <c r="F10">
         <v>2.8</v>
       </c>
-      <c r="F10">
-        <v>6.5</v>
-      </c>
       <c r="G10">
-        <v>10.7</v>
+        <v>6.7</v>
       </c>
       <c r="H10">
-        <v>13.7</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>15.4</v>
+        <v>17.5</v>
       </c>
       <c r="J10">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="K10">
-        <v>23.6</v>
+        <v>35.4</v>
       </c>
       <c r="L10">
-        <v>21.7</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E11">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G11">
-        <v>8.1</v>
+        <v>4.9</v>
       </c>
       <c r="H11">
-        <v>12.6</v>
+        <v>11.4</v>
       </c>
       <c r="I11">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="J11">
-        <v>21.7</v>
+        <v>26.9</v>
       </c>
       <c r="K11">
-        <v>34.5</v>
+        <v>37.8</v>
       </c>
       <c r="L11">
-        <v>15.4</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -2059,35 +2146,38 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>37</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>95.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C2">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -2098,185 +2188,215 @@
       <c r="F2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>91.3</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>98.2</v>
+      </c>
+      <c r="F3">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="G3">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>100</v>
       </c>
-      <c r="C3">
-        <v>98</v>
-      </c>
-      <c r="D3">
-        <v>91.7</v>
-      </c>
-      <c r="E3">
-        <v>99.3</v>
-      </c>
-      <c r="F3">
-        <v>99.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>91.40000000000001</v>
-      </c>
       <c r="C4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>91.60000000000001</v>
       </c>
       <c r="E4">
-        <v>98.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F4">
-        <v>97.89999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>96.2</v>
+      </c>
+      <c r="G4">
+        <v>97.39999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>2.1</v>
+      </c>
+      <c r="D5">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="E5">
+        <v>59.3</v>
+      </c>
+      <c r="F5">
+        <v>77.3</v>
+      </c>
+      <c r="G5">
+        <v>78.60000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>68.7</v>
+      </c>
+      <c r="C6">
+        <v>44.3</v>
+      </c>
+      <c r="D6">
+        <v>86.5</v>
+      </c>
+      <c r="E6">
+        <v>63.4</v>
+      </c>
+      <c r="F6">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="G6">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
-        <v>100</v>
-      </c>
-      <c r="C5">
-        <v>99.2</v>
-      </c>
-      <c r="D5">
-        <v>68.60000000000001</v>
-      </c>
-      <c r="E5">
-        <v>65.5</v>
-      </c>
-      <c r="F5">
-        <v>69.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>2.8</v>
-      </c>
-      <c r="D6">
-        <v>77</v>
-      </c>
-      <c r="E6">
-        <v>62.4</v>
-      </c>
-      <c r="F6">
-        <v>64.09999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="B7">
-        <v>65</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C7">
-        <v>44.4</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D7">
-        <v>85</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E7">
-        <v>63.4</v>
+        <v>66.3</v>
       </c>
       <c r="F7">
-        <v>58.59999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>65.2</v>
+      </c>
+      <c r="G7">
+        <v>65.10000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8">
-        <v>78.90000000000001</v>
+        <v>58.2</v>
       </c>
       <c r="C8">
-        <v>65</v>
+        <v>14.9</v>
       </c>
       <c r="D8">
-        <v>39.90000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="E8">
-        <v>39.90000000000001</v>
+        <v>27.1</v>
       </c>
       <c r="F8">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>43.5</v>
+      </c>
+      <c r="G8">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9">
-        <v>58.9</v>
+        <v>8.4</v>
       </c>
       <c r="C9">
-        <v>14.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D9">
-        <v>1.3</v>
+        <v>37.3</v>
       </c>
       <c r="E9">
-        <v>27.9</v>
+        <v>19.1</v>
       </c>
       <c r="F9">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>20.8</v>
+      </c>
+      <c r="G9">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C10">
         <v>1.7</v>
       </c>
       <c r="D10">
-        <v>0.8999999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="E10">
-        <v>21.4</v>
+        <v>22.7</v>
       </c>
       <c r="F10">
-        <v>22.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>10.1</v>
+      </c>
+      <c r="G10">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>79.60000000000001</v>
       </c>
       <c r="C11">
-        <v>74.3</v>
+        <v>65</v>
       </c>
       <c r="D11">
-        <v>35.6</v>
+        <v>40.6</v>
       </c>
       <c r="E11">
-        <v>21.5</v>
+        <v>44</v>
       </c>
       <c r="F11">
-        <v>15</v>
+        <v>8.9</v>
+      </c>
+      <c r="G11">
+        <v>8.799999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2291,28 +2411,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2320,28 +2440,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2">
-        <v>102</v>
+        <v>107.77</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>113.37</v>
+        <v>116.5</v>
       </c>
       <c r="G2">
-        <v>0.475</v>
+        <v>0.511</v>
       </c>
       <c r="H2">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2349,28 +2469,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3">
+        <v>96.95999999999999</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>117.71</v>
+      </c>
+      <c r="G3">
+        <v>0.511</v>
+      </c>
+      <c r="H3">
+        <v>1.8</v>
+      </c>
+      <c r="I3">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3">
-        <v>129.72</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>113.85</v>
-      </c>
-      <c r="G3">
-        <v>0.55</v>
-      </c>
-      <c r="H3">
-        <v>1.1</v>
-      </c>
-      <c r="I3">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2378,28 +2498,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4">
-        <v>105.53</v>
+        <v>108.78</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>113.2</v>
+        <v>116.39</v>
       </c>
       <c r="G4">
-        <v>0.475</v>
+        <v>0.489</v>
       </c>
       <c r="H4">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2407,28 +2527,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5">
-        <v>100.88</v>
+        <v>112.13</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>112.25</v>
+        <v>116.02</v>
       </c>
       <c r="G5">
-        <v>0.525</v>
+        <v>0.489</v>
       </c>
       <c r="H5">
         <v>0.3</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2436,28 +2556,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>134.34</v>
+        <v>104.19</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>110.2</v>
+        <v>116.9</v>
       </c>
       <c r="G6">
-        <v>0.425</v>
+        <v>0.533</v>
       </c>
       <c r="H6">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2465,28 +2585,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7">
-        <v>107.39</v>
+        <v>129.18</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>115.59</v>
+        <v>114.13</v>
       </c>
       <c r="G7">
-        <v>0.575</v>
+        <v>0.489</v>
       </c>
       <c r="H7">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2494,28 +2614,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>94.40000000000001</v>
+        <v>110.9</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>113.54</v>
+        <v>116.16</v>
       </c>
       <c r="G8">
-        <v>0.475</v>
+        <v>0.533</v>
       </c>
       <c r="H8">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2523,28 +2643,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>108.6</v>
+        <v>112.85</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>112.59</v>
+        <v>115.94</v>
       </c>
       <c r="G9">
-        <v>0.525</v>
+        <v>0.489</v>
       </c>
       <c r="H9">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2552,28 +2672,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>139.3</v>
+        <v>139.13</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>111.94</v>
+        <v>113.02</v>
       </c>
       <c r="G10">
-        <v>0.45</v>
+        <v>0.489</v>
       </c>
       <c r="H10">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2581,28 +2701,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11">
-        <v>106.78</v>
+        <v>134.42</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>112.42</v>
+        <v>113.54</v>
       </c>
       <c r="G11">
-        <v>0.525</v>
+        <v>0.467</v>
       </c>
       <c r="H11">
-        <v>-1.5</v>
+        <v>-2.2</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2617,31 +2737,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2649,16 +2769,16 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D2">
-        <v>139.3025</v>
+        <v>134.422</v>
       </c>
       <c r="E2">
-        <v>557.2099999999999</v>
+        <v>672.1099999999999</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2667,97 +2787,97 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D3">
-        <v>134.345</v>
+        <v>139.13</v>
       </c>
       <c r="E3">
-        <v>537.38</v>
+        <v>695.65</v>
       </c>
       <c r="F3">
-        <v>99.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D4">
-        <v>129.725</v>
+        <v>129.178</v>
       </c>
       <c r="E4">
-        <v>518.9</v>
+        <v>645.89</v>
       </c>
       <c r="F4">
-        <v>96.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C5">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D5">
-        <v>102.0025</v>
+        <v>112.13</v>
       </c>
       <c r="E5">
-        <v>408.01</v>
+        <v>560.65</v>
       </c>
       <c r="F5">
-        <v>69.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G5">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="H5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2765,54 +2885,54 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D6">
-        <v>106.7825</v>
+        <v>112.846</v>
       </c>
       <c r="E6">
-        <v>427.13</v>
+        <v>564.23</v>
       </c>
       <c r="F6">
-        <v>67.60000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G6">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D7">
-        <v>105.5275</v>
+        <v>108.778</v>
       </c>
       <c r="E7">
-        <v>422.11</v>
+        <v>543.89</v>
       </c>
       <c r="F7">
-        <v>58.9</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="G7">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
         <v>81</v>
@@ -2820,60 +2940,60 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D8">
-        <v>108.5975</v>
+        <v>107.774</v>
       </c>
       <c r="E8">
-        <v>434.39</v>
+        <v>538.87</v>
       </c>
       <c r="F8">
-        <v>46.2</v>
+        <v>36.7</v>
       </c>
       <c r="G8">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="H8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C9">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>100.885</v>
+        <v>110.898</v>
       </c>
       <c r="E9">
-        <v>403.54</v>
+        <v>554.49</v>
       </c>
       <c r="F9">
-        <v>24.9</v>
+        <v>23.4</v>
       </c>
       <c r="G9">
-        <v>21.6</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2881,57 +3001,57 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
-        <v>94.39750000000001</v>
+        <v>96.96200000000002</v>
       </c>
       <c r="E10">
-        <v>377.59</v>
+        <v>484.8100000000001</v>
       </c>
       <c r="F10">
-        <v>21.7</v>
+        <v>11.2</v>
       </c>
       <c r="G10">
-        <v>23.6</v>
+        <v>35.4</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D11">
-        <v>107.39</v>
+        <v>104.194</v>
       </c>
       <c r="E11">
-        <v>429.56</v>
+        <v>520.97</v>
       </c>
       <c r="F11">
-        <v>15.4</v>
+        <v>7.8</v>
       </c>
       <c r="G11">
-        <v>34.5</v>
+        <v>37.8</v>
       </c>
       <c r="H11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2946,19 +3066,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2969,16 +3089,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2986,19 +3106,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D3">
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3006,19 +3126,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3026,19 +3146,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3046,7 +3166,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
         <v>51</v>
@@ -3055,10 +3175,10 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3066,19 +3186,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3089,16 +3209,16 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D8">
         <v>-4</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3109,16 +3229,16 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D9">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3129,10 +3249,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D10">
-        <v>-12</v>
+        <v>-17</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -3149,13 +3269,13 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>93</v>
@@ -3168,27 +3288,30 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>100</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -3204,99 +3327,114 @@
       <c r="E2">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="F2">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>-11</v>
+      </c>
+      <c r="C4">
+        <v>-8</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B5">
         <v>0</v>
       </c>
-      <c r="C3">
+      <c r="C5">
         <v>6</v>
       </c>
-      <c r="D3">
+      <c r="D5">
         <v>7</v>
       </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4">
+      <c r="B6">
         <v>6</v>
       </c>
-      <c r="C4">
+      <c r="C6">
         <v>8</v>
       </c>
-      <c r="D4">
+      <c r="D6">
         <v>2</v>
       </c>
-      <c r="E4">
+      <c r="E6">
         <v>7</v>
       </c>
-      <c r="F4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>16</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
+      <c r="F6">
         <v>2</v>
       </c>
-      <c r="B6">
+      <c r="G6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6">
+      <c r="B7">
         <v>2</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
+      <c r="C7">
         <v>2</v>
-      </c>
-      <c r="F6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>-11</v>
-      </c>
-      <c r="C7">
-        <v>-8</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -3304,11 +3442,14 @@
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -3324,11 +3465,14 @@
       <c r="E8">
         <v>-4</v>
       </c>
-      <c r="F8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8">
+        <v>-4</v>
+      </c>
+      <c r="G8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -3344,11 +3488,14 @@
       <c r="E9">
         <v>-12</v>
       </c>
-      <c r="F9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="F9">
+        <v>-8</v>
+      </c>
+      <c r="G9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
@@ -3364,11 +3511,14 @@
       <c r="E10">
         <v>-12</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10">
+        <v>-17</v>
+      </c>
+      <c r="G10" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -3384,7 +3534,10 @@
       <c r="E11">
         <v>-16</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11">
+        <v>-18</v>
+      </c>
+      <c r="G11" t="s">
         <v>93</v>
       </c>
     </row>

--- a/data/leagues/Game of Yards! 2026.xlsx
+++ b/data/leagues/Game of Yards! 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="111">
   <si>
     <t>Groot-o-Matic</t>
   </si>
@@ -55,22 +55,25 @@
     <t>Team HebAchi</t>
   </si>
   <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>4-1-0</t>
-  </si>
-  <si>
-    <t>0-5-0</t>
-  </si>
-  <si>
-    <t>1-4-0</t>
-  </si>
-  <si>
-    <t>5-0-0</t>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>5-1-0</t>
+  </si>
+  <si>
+    <t>0-6-0</t>
+  </si>
+  <si>
+    <t>1-5-0</t>
+  </si>
+  <si>
+    <t>6-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -142,6 +145,9 @@
     <t>Week_6</t>
   </si>
   <si>
+    <t>Week_7</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -163,10 +169,19 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Hayat Khan</t>
+  </si>
+  <si>
+    <t>Harshit Aggarwal</t>
+  </si>
+  <si>
+    <t>Kabir Manocha</t>
+  </si>
+  <si>
     <t>Shihab Chowdhury</t>
   </si>
   <si>
-    <t>Hayat Khan</t>
+    <t>Utkarsh Gupta</t>
   </si>
   <si>
     <t>Vidhi Sethia</t>
@@ -175,21 +190,12 @@
     <t>Pawan Bhambhwani</t>
   </si>
   <si>
-    <t>Kabir Manocha</t>
-  </si>
-  <si>
-    <t>Utkarsh Gupta</t>
-  </si>
-  <si>
-    <t>Harshit Aggarwal</t>
+    <t>Achira Amur</t>
   </si>
   <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
-    <t>Achira Amur</t>
-  </si>
-  <si>
     <t>Saurin Sethia</t>
   </si>
   <si>
@@ -217,63 +223,63 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>10.6-3.4-0.1</t>
-  </si>
-  <si>
-    <t>9.6-4.4-0.1</t>
-  </si>
-  <si>
-    <t>8.6-5.3-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.7-0.1</t>
-  </si>
-  <si>
-    <t>7.3-6.6-0.1</t>
-  </si>
-  <si>
-    <t>6.9-7.1-0.1</t>
-  </si>
-  <si>
-    <t>5.7-8.2-0.1</t>
-  </si>
-  <si>
-    <t>5.0-8.9-0.1</t>
-  </si>
-  <si>
-    <t>4.6-9.3-0.1</t>
-  </si>
-  <si>
-    <t>4.2-9.7-0.1</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>10.8-3.1-0.1</t>
+  </si>
+  <si>
+    <t>9.4-4.5-0.1</t>
+  </si>
+  <si>
+    <t>7.8-6.1-0.1</t>
+  </si>
+  <si>
+    <t>7.9-6.0-0.1</t>
+  </si>
+  <si>
+    <t>7.2-6.8-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.3-0.1</t>
+  </si>
+  <si>
+    <t>6.5-7.4-0.1</t>
+  </si>
+  <si>
+    <t>5.4-8.5-0.1</t>
+  </si>
+  <si>
+    <t>3.9-10.0-0.1</t>
+  </si>
+  <si>
+    <t>4.0-9.9</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
-    <t>10-4</t>
-  </si>
-  <si>
     <t>9-5</t>
   </si>
   <si>
+    <t>8-6</t>
+  </si>
+  <si>
     <t>7-7</t>
   </si>
   <si>
-    <t>8-6</t>
-  </si>
-  <si>
     <t>5-9</t>
   </si>
   <si>
@@ -289,30 +295,30 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
     <t>↑2</t>
   </si>
   <si>
+    <t>↓4</t>
+  </si>
+  <si>
     <t>↑5</t>
   </si>
   <si>
-    <t>↑6</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
     <t>↓5</t>
   </si>
   <si>
-    <t>↓2</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑4</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -326,6 +332,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -753,16 +762,16 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
         <v>10</v>
@@ -771,7 +780,7 @@
         <v>12</v>
       </c>
       <c r="K2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -785,28 +794,28 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
         <v>10</v>
       </c>
       <c r="K3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -820,28 +829,28 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -849,34 +858,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
       <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>11</v>
       </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
       <c r="I5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -887,31 +896,31 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -931,13 +940,13 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
         <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
         <v>12</v>
@@ -946,7 +955,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -954,34 +963,34 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -989,34 +998,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1036,7 +1045,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -1068,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
         <v>12</v>
       </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
       <c r="G11" t="s">
         <v>10</v>
       </c>
       <c r="H11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" t="s">
         <v>12</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>12</v>
-      </c>
-      <c r="J11" t="s">
-        <v>10</v>
-      </c>
-      <c r="K11" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1096,30 +1105,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1205,25 +1214,25 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
       <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5">
         <v>2</v>
       </c>
-      <c r="E5">
-        <v>-8</v>
-      </c>
       <c r="F5">
-        <v>2</v>
+        <v>-13</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1231,25 +1240,25 @@
         <v>4</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>-8</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1257,25 +1266,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1283,25 +1292,25 @@
         <v>6</v>
       </c>
       <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8">
-        <v>-12</v>
-      </c>
       <c r="F8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1309,22 +1318,22 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -1335,24 +1344,76 @@
         <v>8</v>
       </c>
       <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>-12</v>
+      </c>
+      <c r="F10">
+        <v>-4</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
         <v>5</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>-4</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
         <v>3</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D12" t="s">
         <v>1</v>
       </c>
-      <c r="E10">
+      <c r="E12">
         <v>-18</v>
       </c>
-      <c r="F10">
+      <c r="F12">
         <v>-17</v>
       </c>
-      <c r="G10">
+      <c r="G12">
         <v>1</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1368,13 +1429,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1382,13 +1443,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1396,13 +1457,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1410,13 +1471,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1427,10 +1488,10 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1441,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -1455,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -1469,7 +1530,7 @@
         <v>8</v>
       </c>
       <c r="C8">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1483,10 +1544,10 @@
         <v>9</v>
       </c>
       <c r="C9">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1497,10 +1558,10 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1511,10 +1572,10 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1529,16 +1590,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1549,13 +1610,13 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="D2">
-        <v>-0.2999999999999998</v>
+        <v>-0.4000000000000004</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1566,13 +1627,13 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="D3">
-        <v>0.5</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1580,16 +1641,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="D4">
-        <v>-0.1000000000000001</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1597,13 +1658,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="D5">
-        <v>-0.2999999999999998</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1614,16 +1675,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1631,13 +1692,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="D7">
-        <v>-0.6000000000000001</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -1648,16 +1709,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="D8">
-        <v>1.3</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1665,16 +1726,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="D9">
-        <v>0.8999999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1682,16 +1743,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="D10">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1723,40 +1784,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1764,22 +1825,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>55.6</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="C2">
-        <v>32.1</v>
+        <v>23</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="F2">
         <v>0.5</v>
       </c>
       <c r="G2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1802,28 +1863,28 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>31.8</v>
+        <v>25</v>
       </c>
       <c r="C3">
-        <v>35.4</v>
+        <v>42.8</v>
       </c>
       <c r="D3">
-        <v>20.6</v>
+        <v>16.8</v>
       </c>
       <c r="E3">
-        <v>7.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F3">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="G3">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="H3">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1840,189 +1901,189 @@
         <v>0</v>
       </c>
       <c r="B4">
-        <v>10.5</v>
+        <v>3.3</v>
       </c>
       <c r="C4">
-        <v>19.4</v>
+        <v>13.9</v>
       </c>
       <c r="D4">
-        <v>37.2</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>20.7</v>
       </c>
       <c r="F4">
-        <v>8.4</v>
+        <v>14.3</v>
       </c>
       <c r="G4">
-        <v>4.6</v>
+        <v>11.1</v>
       </c>
       <c r="H4">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="I4">
+        <v>2.6</v>
+      </c>
+      <c r="J4">
         <v>0.9</v>
       </c>
-      <c r="J4">
-        <v>0.3</v>
-      </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L4">
-        <v>97.09999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5">
+        <v>1.8</v>
+      </c>
+      <c r="C5">
+        <v>10.7</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>22.3</v>
+      </c>
+      <c r="F5">
+        <v>17.4</v>
+      </c>
+      <c r="G5">
+        <v>13.9</v>
+      </c>
+      <c r="H5">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I5">
+        <v>3.7</v>
+      </c>
+      <c r="J5">
         <v>0.8</v>
       </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-      <c r="D5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>24.2</v>
-      </c>
-      <c r="G5">
-        <v>18.6</v>
-      </c>
-      <c r="H5">
-        <v>11.4</v>
-      </c>
-      <c r="I5">
-        <v>5.6</v>
-      </c>
-      <c r="J5">
-        <v>3.3</v>
-      </c>
       <c r="K5">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="L5">
-        <v>78.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6">
         <v>0.8</v>
       </c>
       <c r="C6">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>13.4</v>
+        <v>15.7</v>
       </c>
       <c r="E6">
-        <v>21.2</v>
+        <v>20.2</v>
       </c>
       <c r="F6">
-        <v>22.4</v>
+        <v>20.1</v>
       </c>
       <c r="G6">
-        <v>15.4</v>
+        <v>16.7</v>
       </c>
       <c r="H6">
-        <v>10.8</v>
+        <v>11.8</v>
       </c>
       <c r="I6">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J6">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="K6">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="L6">
-        <v>78.40000000000001</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="C7">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="D7">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="E7">
-        <v>19.3</v>
+        <v>12.4</v>
       </c>
       <c r="F7">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="G7">
-        <v>21.1</v>
+        <v>18.3</v>
       </c>
       <c r="H7">
-        <v>14.8</v>
+        <v>19.5</v>
       </c>
       <c r="I7">
-        <v>9.1</v>
+        <v>14.6</v>
       </c>
       <c r="J7">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="L7">
-        <v>67.40000000000001</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C8">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="D8">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="E8">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>11.7</v>
+        <v>15.6</v>
       </c>
       <c r="G8">
-        <v>15.6</v>
+        <v>20.5</v>
       </c>
       <c r="H8">
-        <v>20.2</v>
+        <v>21.8</v>
       </c>
       <c r="I8">
-        <v>20.1</v>
+        <v>14.4</v>
       </c>
       <c r="J8">
-        <v>14.1</v>
+        <v>7.5</v>
       </c>
       <c r="K8">
-        <v>8.9</v>
+        <v>2.7</v>
       </c>
       <c r="L8">
-        <v>36.7</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2033,39 +2094,39 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D9">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="E9">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F9">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="G9">
-        <v>11.7</v>
+        <v>13.7</v>
       </c>
       <c r="H9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="I9">
-        <v>23.9</v>
+        <v>31.7</v>
       </c>
       <c r="J9">
-        <v>19.7</v>
+        <v>14.7</v>
       </c>
       <c r="K9">
-        <v>14</v>
+        <v>6.9</v>
       </c>
       <c r="L9">
-        <v>23.4</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2074,69 +2135,69 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="F10">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="G10">
-        <v>6.7</v>
+        <v>2.3</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="I10">
-        <v>17.5</v>
+        <v>16.3</v>
       </c>
       <c r="J10">
-        <v>25.9</v>
+        <v>37.5</v>
       </c>
       <c r="K10">
-        <v>35.4</v>
+        <v>35.8</v>
       </c>
       <c r="L10">
-        <v>11.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D11">
         <v>0.2</v>
       </c>
       <c r="E11">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F11">
+        <v>0.6</v>
+      </c>
+      <c r="G11">
+        <v>1.5</v>
+      </c>
+      <c r="H11">
+        <v>4.7</v>
+      </c>
+      <c r="I11">
+        <v>10.1</v>
+      </c>
+      <c r="J11">
+        <v>30.8</v>
+      </c>
+      <c r="K11">
+        <v>51.9</v>
+      </c>
+      <c r="L11">
         <v>2.5</v>
-      </c>
-      <c r="G11">
-        <v>4.9</v>
-      </c>
-      <c r="H11">
-        <v>11.4</v>
-      </c>
-      <c r="I11">
-        <v>16.1</v>
-      </c>
-      <c r="J11">
-        <v>26.9</v>
-      </c>
-      <c r="K11">
-        <v>37.8</v>
-      </c>
-      <c r="L11">
-        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -2146,38 +2207,41 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>39</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>94.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="C2">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -2186,18 +2250,21 @@
         <v>100</v>
       </c>
       <c r="F2">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G2">
         <v>100</v>
       </c>
-      <c r="G2">
-        <v>99.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>91.3</v>
+        <v>92.10000000000001</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -2206,197 +2273,224 @@
         <v>100</v>
       </c>
       <c r="E3">
-        <v>98.2</v>
+        <v>97.8</v>
       </c>
       <c r="F3">
+        <v>99.2</v>
+      </c>
+      <c r="G3">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="H3">
         <v>99.09999999999999</v>
       </c>
-      <c r="G3">
-        <v>99.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C4">
-        <v>97.5</v>
+        <v>98</v>
       </c>
       <c r="D4">
-        <v>91.60000000000001</v>
+        <v>93</v>
       </c>
       <c r="E4">
+        <v>99.7</v>
+      </c>
+      <c r="F4">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="G4">
+        <v>91.5</v>
+      </c>
+      <c r="H4">
+        <v>89.60000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
         <v>99.90000000000001</v>
       </c>
-      <c r="F4">
-        <v>96.2</v>
-      </c>
-      <c r="G4">
-        <v>97.39999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
+      <c r="C5">
+        <v>99</v>
+      </c>
+      <c r="D5">
+        <v>65.2</v>
+      </c>
+      <c r="E5">
+        <v>63.4</v>
+      </c>
+      <c r="F5">
+        <v>61.6</v>
+      </c>
+      <c r="G5">
+        <v>83.7</v>
+      </c>
+      <c r="H5">
+        <v>86.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>58.09999999999999</v>
+      </c>
+      <c r="C6">
+        <v>12.9</v>
+      </c>
+      <c r="D6">
+        <v>0.8</v>
+      </c>
+      <c r="E6">
+        <v>27.3</v>
+      </c>
+      <c r="F6">
+        <v>45.5</v>
+      </c>
+      <c r="G6">
+        <v>82.5</v>
+      </c>
+      <c r="H6">
+        <v>80.60000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B7">
         <v>0</v>
       </c>
-      <c r="C5">
-        <v>2.1</v>
-      </c>
-      <c r="D5">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="E5">
-        <v>59.3</v>
-      </c>
-      <c r="F5">
-        <v>77.3</v>
-      </c>
-      <c r="G5">
-        <v>78.60000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
+      <c r="C7">
+        <v>2.9</v>
+      </c>
+      <c r="D7">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="E7">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F7">
+        <v>80.10000000000001</v>
+      </c>
+      <c r="G7">
+        <v>52.6</v>
+      </c>
+      <c r="H7">
+        <v>60.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>68.7</v>
-      </c>
-      <c r="C6">
-        <v>44.3</v>
-      </c>
-      <c r="D6">
-        <v>86.5</v>
-      </c>
-      <c r="E6">
+      <c r="B8">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="C8">
+        <v>46.5</v>
+      </c>
+      <c r="D8">
+        <v>83.7</v>
+      </c>
+      <c r="E8">
         <v>63.4</v>
       </c>
-      <c r="F6">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="G6">
-        <v>76.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="C7">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="D7">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="E7">
-        <v>66.3</v>
-      </c>
-      <c r="F7">
-        <v>65.2</v>
-      </c>
-      <c r="G7">
-        <v>65.10000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>58.2</v>
-      </c>
-      <c r="C8">
-        <v>14.9</v>
-      </c>
-      <c r="D8">
-        <v>1.4</v>
-      </c>
-      <c r="E8">
-        <v>27.1</v>
-      </c>
       <c r="F8">
-        <v>43.5</v>
+        <v>76.7</v>
       </c>
       <c r="G8">
-        <v>41.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>47.2</v>
+      </c>
+      <c r="H8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B9">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C9">
-        <v>75.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="D9">
-        <v>37.3</v>
+        <v>37.5</v>
       </c>
       <c r="E9">
-        <v>19.1</v>
+        <v>20.1</v>
       </c>
       <c r="F9">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="G9">
-        <v>23.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>35.6</v>
+      </c>
+      <c r="H9">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>80.80000000000001</v>
+      </c>
+      <c r="C10">
+        <v>68.5</v>
+      </c>
+      <c r="D10">
+        <v>41.4</v>
+      </c>
+      <c r="E10">
+        <v>38.3</v>
+      </c>
+      <c r="F10">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G10">
+        <v>4.9</v>
+      </c>
+      <c r="H10">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>0.1</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>1.7</v>
       </c>
-      <c r="D10">
-        <v>0.8</v>
-      </c>
-      <c r="E10">
-        <v>22.7</v>
-      </c>
-      <c r="F10">
-        <v>10.1</v>
-      </c>
-      <c r="G10">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11">
-        <v>79.60000000000001</v>
-      </c>
-      <c r="C11">
-        <v>65</v>
-      </c>
       <c r="D11">
-        <v>40.6</v>
+        <v>0.5</v>
       </c>
       <c r="E11">
-        <v>44</v>
+        <v>25.6</v>
       </c>
       <c r="F11">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G11">
-        <v>8.799999999999999</v>
+        <v>2.1</v>
+      </c>
+      <c r="H11">
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>
@@ -2411,28 +2505,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2440,28 +2534,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>107.77</v>
+        <v>89.62</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2">
-        <v>116.5</v>
+        <v>116.02</v>
       </c>
       <c r="G2">
-        <v>0.511</v>
+        <v>0.542</v>
       </c>
       <c r="H2">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2469,28 +2563,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>96.95999999999999</v>
+        <v>108.71</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>117.71</v>
+        <v>116.02</v>
       </c>
       <c r="G3">
-        <v>0.511</v>
+        <v>0.542</v>
       </c>
       <c r="H3">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2498,28 +2592,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>108.78</v>
+        <v>102.03</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>116.39</v>
+        <v>113.44</v>
       </c>
       <c r="G4">
-        <v>0.489</v>
+        <v>0.542</v>
       </c>
       <c r="H4">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2527,28 +2621,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5">
+        <v>116.95</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>113.44</v>
+      </c>
+      <c r="G5">
+        <v>0.542</v>
+      </c>
+      <c r="H5">
+        <v>1.4</v>
+      </c>
+      <c r="I5">
         <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5">
-        <v>112.13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>116.02</v>
-      </c>
-      <c r="G5">
-        <v>0.489</v>
-      </c>
-      <c r="H5">
-        <v>0.3</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2556,28 +2650,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>104.19</v>
+        <v>123.08</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>116.9</v>
+        <v>111.66</v>
       </c>
       <c r="G6">
-        <v>0.533</v>
+        <v>0.479</v>
       </c>
       <c r="H6">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2585,28 +2679,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>129.18</v>
+        <v>110.13</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>114.13</v>
+        <v>111.66</v>
       </c>
       <c r="G7">
-        <v>0.489</v>
+        <v>0.479</v>
       </c>
       <c r="H7">
-        <v>-0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2614,28 +2708,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D8">
-        <v>110.9</v>
+        <v>105.2</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>116.16</v>
+        <v>111.21</v>
       </c>
       <c r="G8">
-        <v>0.533</v>
+        <v>0.479</v>
       </c>
       <c r="H8">
-        <v>-0.9</v>
+        <v>0.1</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2643,28 +2737,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9">
-        <v>112.85</v>
+        <v>131.67</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>115.94</v>
+        <v>111.21</v>
       </c>
       <c r="G9">
-        <v>0.489</v>
+        <v>0.479</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2672,28 +2766,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10">
-        <v>139.13</v>
+        <v>106.79</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10">
-        <v>113.02</v>
+        <v>110.92</v>
       </c>
       <c r="G10">
-        <v>0.489</v>
+        <v>0.458</v>
       </c>
       <c r="H10">
-        <v>-1.2</v>
+        <v>-3.8</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2704,25 +2798,25 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>134.42</v>
+        <v>132.33</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>113.54</v>
+        <v>110.92</v>
       </c>
       <c r="G11">
-        <v>0.467</v>
+        <v>0.458</v>
       </c>
       <c r="H11">
-        <v>-2.2</v>
+        <v>-3.8</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2737,31 +2831,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2769,16 +2863,16 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D2">
-        <v>134.422</v>
+        <v>132.3316666666666</v>
       </c>
       <c r="E2">
-        <v>672.1099999999999</v>
+        <v>793.9899999999999</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2787,10 +2881,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2798,16 +2892,16 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>139.13</v>
+        <v>131.67</v>
       </c>
       <c r="E3">
-        <v>695.65</v>
+        <v>790.02</v>
       </c>
       <c r="F3">
         <v>99.09999999999999</v>
@@ -2816,10 +2910,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2827,144 +2921,144 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C4">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
-        <v>129.178</v>
+        <v>123.0783333333333</v>
       </c>
       <c r="E4">
-        <v>645.89</v>
+        <v>738.47</v>
       </c>
       <c r="F4">
-        <v>97.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>112.13</v>
+        <v>110.1283333333333</v>
       </c>
       <c r="E5">
-        <v>560.65</v>
+        <v>660.77</v>
       </c>
       <c r="F5">
-        <v>78.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G5">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C6">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>112.846</v>
+        <v>116.9516666666667</v>
       </c>
       <c r="E6">
-        <v>564.23</v>
+        <v>701.71</v>
       </c>
       <c r="F6">
-        <v>78.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="G6">
-        <v>1.1</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C7">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>108.778</v>
+        <v>106.79</v>
       </c>
       <c r="E7">
-        <v>543.89</v>
+        <v>640.74</v>
       </c>
       <c r="F7">
-        <v>67.40000000000001</v>
+        <v>58.09999999999999</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>107.774</v>
+        <v>105.2033333333333</v>
       </c>
       <c r="E8">
-        <v>538.87</v>
+        <v>631.22</v>
       </c>
       <c r="F8">
-        <v>36.7</v>
+        <v>53.6</v>
       </c>
       <c r="G8">
-        <v>8.9</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2972,86 +3066,86 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>110.898</v>
+        <v>108.7083333333333</v>
       </c>
       <c r="E9">
-        <v>554.49</v>
+        <v>652.25</v>
       </c>
       <c r="F9">
-        <v>23.4</v>
+        <v>27.2</v>
       </c>
       <c r="G9">
-        <v>14</v>
+        <v>6.9</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C10">
-        <v>0.4</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D10">
-        <v>96.96200000000002</v>
+        <v>102.0333333333333</v>
       </c>
       <c r="E10">
-        <v>484.8100000000001</v>
+        <v>612.2</v>
       </c>
       <c r="F10">
-        <v>11.2</v>
+        <v>3.6</v>
       </c>
       <c r="G10">
-        <v>35.4</v>
+        <v>35.8</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C11">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D11">
-        <v>104.194</v>
+        <v>89.61833333333334</v>
       </c>
       <c r="E11">
-        <v>520.97</v>
+        <v>537.71</v>
       </c>
       <c r="F11">
-        <v>7.8</v>
+        <v>2.5</v>
       </c>
       <c r="G11">
-        <v>37.8</v>
+        <v>51.9</v>
       </c>
       <c r="H11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -3066,19 +3160,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3089,16 +3183,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3106,19 +3200,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3126,19 +3220,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3149,16 +3243,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3169,16 +3263,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3192,13 +3286,13 @@
         <v>50</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3206,19 +3300,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3226,10 +3320,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D9">
         <v>-8</v>
@@ -3246,19 +3340,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D10">
-        <v>-17</v>
+        <v>-13</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3266,19 +3360,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11">
-        <v>-18</v>
+        <v>-22</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3288,30 +3382,33 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>103</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -3330,57 +3427,66 @@
       <c r="F2">
         <v>19</v>
       </c>
-      <c r="G2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="G2">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>-11</v>
+      </c>
+      <c r="C3">
+        <v>-8</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>5</v>
       </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-      <c r="D3">
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
         <v>16</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>-11</v>
-      </c>
-      <c r="C4">
-        <v>-8</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
       <c r="F4">
-        <v>8</v>
-      </c>
-      <c r="G4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -3399,11 +3505,14 @@
       <c r="F5">
         <v>7</v>
       </c>
-      <c r="G5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -3422,11 +3531,14 @@
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -3445,100 +3557,115 @@
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>-4</v>
+      </c>
+      <c r="E8">
+        <v>-12</v>
+      </c>
+      <c r="F8">
+        <v>-8</v>
+      </c>
+      <c r="G8">
+        <v>-5</v>
+      </c>
+      <c r="H8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>4</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>-5</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>-1</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>-4</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>-4</v>
       </c>
-      <c r="G8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>-4</v>
-      </c>
-      <c r="E9">
-        <v>-12</v>
-      </c>
-      <c r="F9">
+      <c r="G9">
         <v>-8</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="C10">
         <v>-12</v>
       </c>
       <c r="D10">
-        <v>-12</v>
+        <v>-20</v>
       </c>
       <c r="E10">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="F10">
-        <v>-17</v>
-      </c>
-      <c r="G10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>-18</v>
+      </c>
+      <c r="G10">
+        <v>-13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="C11">
         <v>-12</v>
       </c>
       <c r="D11">
-        <v>-20</v>
+        <v>-12</v>
       </c>
       <c r="E11">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="F11">
-        <v>-18</v>
-      </c>
-      <c r="G11" t="s">
-        <v>93</v>
+        <v>-17</v>
+      </c>
+      <c r="G11">
+        <v>-22</v>
+      </c>
+      <c r="H11" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Game of Yards! 2026.xlsx
+++ b/data/leagues/Game of Yards! 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="114">
   <si>
     <t>Groot-o-Matic</t>
   </si>
@@ -55,25 +55,28 @@
     <t>Team HebAchi</t>
   </si>
   <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>5-1-0</t>
-  </si>
-  <si>
-    <t>0-6-0</t>
-  </si>
-  <si>
-    <t>1-5-0</t>
-  </si>
-  <si>
-    <t>6-0-0</t>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
+  </si>
+  <si>
+    <t>0-7-0</t>
+  </si>
+  <si>
+    <t>1-6-0</t>
+  </si>
+  <si>
+    <t>7-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -148,6 +151,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -169,36 +175,36 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Utkarsh Gupta</t>
+  </si>
+  <si>
     <t>Hayat Khan</t>
   </si>
   <si>
     <t>Harshit Aggarwal</t>
   </si>
   <si>
+    <t>Achira Amur</t>
+  </si>
+  <si>
     <t>Kabir Manocha</t>
   </si>
   <si>
     <t>Shihab Chowdhury</t>
   </si>
   <si>
-    <t>Utkarsh Gupta</t>
-  </si>
-  <si>
     <t>Vidhi Sethia</t>
   </si>
   <si>
     <t>Pawan Bhambhwani</t>
   </si>
   <si>
-    <t>Achira Amur</t>
+    <t>Saurin Sethia</t>
   </si>
   <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
-    <t>Saurin Sethia</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -223,52 +229,49 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>10.8-3.1-0.1</t>
-  </si>
-  <si>
-    <t>9.4-4.5-0.1</t>
-  </si>
-  <si>
-    <t>7.8-6.1-0.1</t>
-  </si>
-  <si>
-    <t>7.9-6.0-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.8-0.1</t>
-  </si>
-  <si>
-    <t>6.7-7.3-0.1</t>
-  </si>
-  <si>
-    <t>6.5-7.4-0.1</t>
-  </si>
-  <si>
-    <t>5.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>3.9-10.0-0.1</t>
-  </si>
-  <si>
-    <t>4.0-9.9</t>
-  </si>
-  <si>
-    <t>11-3</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>9.9-4.1-0.1</t>
+  </si>
+  <si>
+    <t>8.5-5.4-0.1</t>
+  </si>
+  <si>
+    <t>8.7-5.2-0.1</t>
+  </si>
+  <si>
+    <t>8.0-5.9-0.1</t>
+  </si>
+  <si>
+    <t>7.6-6.3-0.1</t>
+  </si>
+  <si>
+    <t>7.5-6.5-0.1</t>
+  </si>
+  <si>
+    <t>6.4-7.6-0.1</t>
+  </si>
+  <si>
+    <t>4.9-9.1-0.1</t>
+  </si>
+  <si>
+    <t>4.8-9.1-0.1</t>
+  </si>
+  <si>
+    <t>3.5-10.5</t>
+  </si>
+  <si>
+    <t>10-4</t>
   </si>
   <si>
     <t>9-5</t>
@@ -280,10 +283,13 @@
     <t>7-7</t>
   </si>
   <si>
+    <t>6-8</t>
+  </si>
+  <si>
     <t>5-9</t>
   </si>
   <si>
-    <t>4-10</t>
+    <t>3-11</t>
   </si>
   <si>
     <t>Owners</t>
@@ -295,28 +301,28 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↓2</t>
-  </si>
-  <si>
-    <t>↑2</t>
+    <t>↑11</t>
   </si>
   <si>
     <t>↓4</t>
   </si>
   <si>
-    <t>↑5</t>
-  </si>
-  <si>
-    <t>↓5</t>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↓9</t>
+  </si>
+  <si>
+    <t>↓10</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -335,6 +341,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -756,31 +765,31 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
       </c>
       <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" t="s">
-        <v>10</v>
-      </c>
       <c r="J2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" t="s">
         <v>12</v>
-      </c>
-      <c r="K2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -794,28 +803,28 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -826,31 +835,31 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
         <v>10</v>
       </c>
       <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" t="s">
         <v>12</v>
-      </c>
-      <c r="J4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -861,10 +870,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -876,13 +885,13 @@
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" t="s">
         <v>10</v>
@@ -896,13 +905,13 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -911,16 +920,16 @@
         <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" t="s">
         <v>12</v>
       </c>
-      <c r="J6" t="s">
-        <v>10</v>
-      </c>
       <c r="K6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -928,34 +937,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
       <c r="I7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" t="s">
         <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -963,22 +972,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
@@ -998,19 +1007,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
         <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
@@ -1019,10 +1028,10 @@
         <v>10</v>
       </c>
       <c r="I9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" t="s">
         <v>12</v>
-      </c>
-      <c r="J9" t="s">
-        <v>10</v>
       </c>
       <c r="K9" t="s">
         <v>13</v>
@@ -1033,13 +1042,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -1051,16 +1060,16 @@
         <v>11</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" t="s">
         <v>12</v>
       </c>
-      <c r="J10" t="s">
-        <v>10</v>
-      </c>
       <c r="K10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1068,22 +1077,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
       <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
         <v>12</v>
-      </c>
-      <c r="G11" t="s">
-        <v>10</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
@@ -1092,10 +1101,10 @@
         <v>13</v>
       </c>
       <c r="J11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1105,30 +1114,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1162,22 +1171,22 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>-12</v>
+        <v>-6</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
         <v>7</v>
@@ -1188,25 +1197,25 @@
         <v>2</v>
       </c>
       <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
       <c r="E4">
-        <v>16</v>
+        <v>-12</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1214,25 +1223,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="F5">
-        <v>-13</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1240,22 +1249,22 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
-        <v>2</v>
-      </c>
       <c r="E6">
-        <v>-8</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
         <v>5</v>
@@ -1266,25 +1275,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>-13</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1292,25 +1301,25 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="F8">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1318,25 +1327,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1344,25 +1353,25 @@
         <v>8</v>
       </c>
       <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10">
         <v>4</v>
       </c>
-      <c r="C10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10">
-        <v>-12</v>
-      </c>
       <c r="F10">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1370,22 +1379,22 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -1396,25 +1405,51 @@
         <v>10</v>
       </c>
       <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>-12</v>
+      </c>
+      <c r="F12">
+        <v>-4</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13">
         <v>5</v>
       </c>
-      <c r="C12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>-18</v>
-      </c>
-      <c r="F12">
-        <v>-17</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12" t="s">
-        <v>3</v>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>-4</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1429,13 +1464,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1443,13 +1478,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1457,13 +1492,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1474,7 +1509,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1485,13 +1520,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1499,13 +1534,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1513,13 +1548,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1527,10 +1562,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1541,13 +1576,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1558,10 +1593,10 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1572,7 +1607,7 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1590,16 +1625,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1610,10 +1645,10 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="D2">
-        <v>-0.4000000000000004</v>
+        <v>-0.09999999999999964</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -1627,13 +1662,13 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="D3">
-        <v>0.09999999999999964</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1641,16 +1676,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="D4">
-        <v>-0.7000000000000002</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1658,16 +1693,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D5">
-        <v>0.2999999999999998</v>
+        <v>-1.2</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1675,16 +1710,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1692,13 +1727,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="D7">
-        <v>-0.1000000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -1709,16 +1744,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="D8">
-        <v>-0.2000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1729,13 +1764,13 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="D9">
-        <v>-0.5</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1746,13 +1781,13 @@
         <v>2</v>
       </c>
       <c r="C10">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="D10">
-        <v>1.2</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1784,40 +1819,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1825,25 +1860,25 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>68.59999999999999</v>
+        <v>59.2</v>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="E2">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="F2">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1855,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>100</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1863,104 +1898,104 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>25</v>
+        <v>18.9</v>
       </c>
       <c r="C3">
-        <v>42.8</v>
+        <v>25.6</v>
       </c>
       <c r="D3">
-        <v>16.8</v>
+        <v>20.4</v>
       </c>
       <c r="E3">
-        <v>8.699999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="F3">
-        <v>3.9</v>
+        <v>12.7</v>
       </c>
       <c r="G3">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="H3">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="I3">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C4">
-        <v>13.9</v>
+        <v>19.9</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>20.7</v>
+        <v>19.3</v>
       </c>
       <c r="F4">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="I4">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J4">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="K4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>90.3</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>1.8</v>
+        <v>6.6</v>
       </c>
       <c r="C5">
-        <v>10.7</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>17.6</v>
       </c>
       <c r="E5">
-        <v>22.3</v>
+        <v>19.3</v>
       </c>
       <c r="F5">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="G5">
-        <v>13.9</v>
+        <v>12.9</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J5">
         <v>0.8</v>
@@ -1969,45 +2004,45 @@
         <v>0.1</v>
       </c>
       <c r="L5">
-        <v>86.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B6">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>10.4</v>
       </c>
       <c r="D6">
-        <v>15.7</v>
+        <v>14.2</v>
       </c>
       <c r="E6">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="F6">
-        <v>20.1</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>16.7</v>
+        <v>14.7</v>
       </c>
       <c r="H6">
-        <v>11.8</v>
+        <v>9.6</v>
       </c>
       <c r="I6">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="J6">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="K6">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="L6">
-        <v>79.5</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2015,37 +2050,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="C7">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="D7">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="E7">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="F7">
-        <v>18.8</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>18.3</v>
+        <v>23.1</v>
       </c>
       <c r="H7">
-        <v>19.5</v>
+        <v>15.7</v>
       </c>
       <c r="I7">
-        <v>14.6</v>
+        <v>6.9</v>
       </c>
       <c r="J7">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="K7">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="L7">
-        <v>58.1</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2053,37 +2088,37 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C8">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="F8">
-        <v>15.6</v>
+        <v>11.9</v>
       </c>
       <c r="G8">
-        <v>20.5</v>
+        <v>18.9</v>
       </c>
       <c r="H8">
-        <v>21.8</v>
+        <v>29.3</v>
       </c>
       <c r="I8">
-        <v>14.4</v>
+        <v>17.5</v>
       </c>
       <c r="J8">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="K8">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="L8">
-        <v>53.6</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2094,34 +2129,34 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="E9">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="F9">
+        <v>4.1</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>16.4</v>
+      </c>
+      <c r="I9">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>31.4</v>
+      </c>
+      <c r="K9">
         <v>7.6</v>
       </c>
-      <c r="G9">
-        <v>13.7</v>
-      </c>
-      <c r="H9">
-        <v>19.5</v>
-      </c>
-      <c r="I9">
-        <v>31.7</v>
-      </c>
-      <c r="J9">
-        <v>14.7</v>
-      </c>
-      <c r="K9">
-        <v>6.9</v>
-      </c>
       <c r="L9">
-        <v>27.2</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2138,28 +2173,28 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="F10">
         <v>1.2</v>
       </c>
       <c r="G10">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="H10">
-        <v>6.8</v>
+        <v>12.9</v>
       </c>
       <c r="I10">
-        <v>16.3</v>
+        <v>29.4</v>
       </c>
       <c r="J10">
-        <v>37.5</v>
+        <v>38.4</v>
       </c>
       <c r="K10">
-        <v>35.8</v>
+        <v>12.7</v>
       </c>
       <c r="L10">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2170,34 +2205,34 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>0.2</v>
       </c>
-      <c r="E11">
-        <v>0.1</v>
-      </c>
-      <c r="F11">
-        <v>0.6</v>
-      </c>
-      <c r="G11">
-        <v>1.5</v>
-      </c>
       <c r="H11">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="I11">
-        <v>10.1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>30.8</v>
+        <v>15.8</v>
       </c>
       <c r="K11">
-        <v>51.9</v>
+        <v>76.7</v>
       </c>
       <c r="L11">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -2207,41 +2242,44 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>41</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>93.5</v>
+        <v>93.7</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -2250,21 +2288,24 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
       <c r="H2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I2">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>92.10000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -2273,201 +2314,225 @@
         <v>100</v>
       </c>
       <c r="E3">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="F3">
-        <v>99.2</v>
+        <v>99.7</v>
       </c>
       <c r="G3">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="H3">
-        <v>99.09999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>96.2</v>
+      </c>
+      <c r="I3">
+        <v>96.59999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>99.90000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C4">
-        <v>98</v>
+        <v>99.5</v>
       </c>
       <c r="D4">
-        <v>93</v>
+        <v>65.2</v>
       </c>
       <c r="E4">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F4">
+        <v>65.5</v>
+      </c>
+      <c r="G4">
+        <v>83.89999999999999</v>
+      </c>
+      <c r="H4">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="I4">
+        <v>92.30000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>60.3</v>
+      </c>
+      <c r="C5">
+        <v>13.8</v>
+      </c>
+      <c r="D5">
+        <v>1.5</v>
+      </c>
+      <c r="E5">
+        <v>26.4</v>
+      </c>
+      <c r="F5">
+        <v>42.1</v>
+      </c>
+      <c r="G5">
+        <v>83</v>
+      </c>
+      <c r="H5">
+        <v>89.7</v>
+      </c>
+      <c r="I5">
+        <v>88.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>98.5</v>
+      </c>
+      <c r="D6">
+        <v>93.30000000000001</v>
+      </c>
+      <c r="E6">
         <v>99.7</v>
       </c>
-      <c r="F4">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="G4">
-        <v>91.5</v>
-      </c>
-      <c r="H4">
-        <v>89.60000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="C5">
-        <v>99</v>
-      </c>
-      <c r="D5">
-        <v>65.2</v>
-      </c>
-      <c r="E5">
-        <v>63.4</v>
-      </c>
-      <c r="F5">
-        <v>61.6</v>
-      </c>
-      <c r="G5">
-        <v>83.7</v>
-      </c>
-      <c r="H5">
-        <v>86.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>58.09999999999999</v>
-      </c>
-      <c r="C6">
-        <v>12.9</v>
-      </c>
-      <c r="D6">
-        <v>0.8</v>
-      </c>
-      <c r="E6">
-        <v>27.3</v>
-      </c>
       <c r="F6">
-        <v>45.5</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="G6">
+        <v>90.8</v>
+      </c>
+      <c r="H6">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="I6">
         <v>82.5</v>
       </c>
-      <c r="H6">
-        <v>80.60000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="D7">
-        <v>77.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="E7">
-        <v>64.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="F7">
-        <v>80.10000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="G7">
-        <v>52.6</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="H7">
-        <v>60.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>72</v>
+      </c>
+      <c r="I7">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B8">
-        <v>66.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="C8">
-        <v>46.5</v>
+        <v>44.2</v>
       </c>
       <c r="D8">
-        <v>83.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="E8">
-        <v>63.4</v>
+        <v>62.3</v>
       </c>
       <c r="F8">
-        <v>76.7</v>
+        <v>77.8</v>
       </c>
       <c r="G8">
-        <v>47.2</v>
+        <v>47.8</v>
       </c>
       <c r="H8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>44.5</v>
+      </c>
+      <c r="I8">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B9">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C9">
-        <v>70.5</v>
+        <v>72.5</v>
       </c>
       <c r="D9">
-        <v>37.5</v>
+        <v>36.4</v>
       </c>
       <c r="E9">
-        <v>20.1</v>
+        <v>21.6</v>
       </c>
       <c r="F9">
-        <v>21.5</v>
+        <v>22.4</v>
       </c>
       <c r="G9">
-        <v>35.6</v>
+        <v>32.7</v>
       </c>
       <c r="H9">
-        <v>25.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>13.6</v>
+      </c>
+      <c r="I9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B10">
-        <v>80.80000000000001</v>
+        <v>81</v>
       </c>
       <c r="C10">
-        <v>68.5</v>
+        <v>67.7</v>
       </c>
       <c r="D10">
-        <v>41.4</v>
+        <v>38.1</v>
       </c>
       <c r="E10">
-        <v>38.3</v>
+        <v>39.5</v>
       </c>
       <c r="F10">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="G10">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H10">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>7.6</v>
+      </c>
+      <c r="I10">
+        <v>7.000000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -2475,22 +2540,25 @@
         <v>0.1</v>
       </c>
       <c r="C11">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="E11">
-        <v>25.6</v>
+        <v>24.4</v>
       </c>
       <c r="F11">
-        <v>9.199999999999999</v>
+        <v>9.700000000000001</v>
       </c>
       <c r="G11">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="H11">
-        <v>2.3</v>
+        <v>0.3</v>
+      </c>
+      <c r="I11">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -2505,28 +2573,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2534,28 +2602,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>89.62</v>
+        <v>116.23</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>116.02</v>
+        <v>114.25</v>
       </c>
       <c r="G2">
-        <v>0.542</v>
+        <v>0.49</v>
       </c>
       <c r="H2">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2563,28 +2631,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>108.71</v>
+        <v>82.45</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>116.02</v>
+        <v>114.36</v>
       </c>
       <c r="G3">
-        <v>0.542</v>
+        <v>0.551</v>
       </c>
       <c r="H3">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2592,28 +2660,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4">
-        <v>102.03</v>
+        <v>108.93</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>113.44</v>
+        <v>116.17</v>
       </c>
       <c r="G4">
-        <v>0.542</v>
+        <v>0.592</v>
       </c>
       <c r="H4">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2621,28 +2689,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5">
-        <v>116.95</v>
+        <v>125.63</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>113.44</v>
+        <v>108.29</v>
       </c>
       <c r="G5">
-        <v>0.542</v>
+        <v>0.49</v>
       </c>
       <c r="H5">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2650,28 +2718,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D6">
-        <v>123.08</v>
+        <v>103.61</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>111.66</v>
+        <v>111.26</v>
       </c>
       <c r="G6">
-        <v>0.479</v>
+        <v>0.551</v>
       </c>
       <c r="H6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2679,28 +2747,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7">
+        <v>116.79</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>108.88</v>
+      </c>
+      <c r="G7">
+        <v>0.51</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7">
-        <v>110.13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7">
-        <v>111.66</v>
-      </c>
-      <c r="G7">
-        <v>0.479</v>
-      </c>
-      <c r="H7">
-        <v>0.1</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2708,28 +2776,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D8">
-        <v>105.2</v>
+        <v>109.75</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>111.21</v>
+        <v>107.81</v>
       </c>
       <c r="G8">
-        <v>0.479</v>
+        <v>0.429</v>
       </c>
       <c r="H8">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2737,28 +2805,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9">
-        <v>131.67</v>
+        <v>107.69</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9">
-        <v>111.21</v>
+        <v>109.32</v>
       </c>
       <c r="G9">
-        <v>0.479</v>
+        <v>0.49</v>
       </c>
       <c r="H9">
-        <v>0.1</v>
+        <v>-3.6</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2766,28 +2834,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10">
-        <v>106.79</v>
+        <v>127.48</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>110.92</v>
+        <v>108.76</v>
       </c>
       <c r="G10">
-        <v>0.458</v>
+        <v>0.429</v>
       </c>
       <c r="H10">
-        <v>-3.8</v>
+        <v>-4.4</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2795,28 +2863,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D11">
-        <v>132.33</v>
+        <v>109.6</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>110.92</v>
+        <v>109.06</v>
       </c>
       <c r="G11">
-        <v>0.458</v>
+        <v>0.469</v>
       </c>
       <c r="H11">
-        <v>-3.8</v>
+        <v>-5.3</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2831,31 +2899,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2863,28 +2931,28 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D2">
-        <v>132.3316666666666</v>
+        <v>127.4842857142857</v>
       </c>
       <c r="E2">
-        <v>793.9899999999999</v>
+        <v>892.3899999999999</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2892,54 +2960,54 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D3">
-        <v>131.67</v>
+        <v>125.6342857142857</v>
       </c>
       <c r="E3">
-        <v>790.02</v>
+        <v>879.4399999999999</v>
       </c>
       <c r="F3">
-        <v>99.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D4">
-        <v>123.0783333333333</v>
+        <v>109.7485714285714</v>
       </c>
       <c r="E4">
-        <v>738.47</v>
+        <v>768.24</v>
       </c>
       <c r="F4">
-        <v>90.3</v>
+        <v>93.2</v>
       </c>
       <c r="G4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I4" t="s">
         <v>83</v>
@@ -2947,57 +3015,57 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D5">
-        <v>110.1283333333333</v>
+        <v>116.7857142857143</v>
       </c>
       <c r="E5">
-        <v>660.77</v>
+        <v>817.5</v>
       </c>
       <c r="F5">
-        <v>86.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G5">
         <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D6">
-        <v>116.9516666666667</v>
+        <v>116.2342857142857</v>
       </c>
       <c r="E6">
-        <v>701.71</v>
+        <v>813.64</v>
       </c>
       <c r="F6">
-        <v>79.5</v>
+        <v>83.5</v>
       </c>
       <c r="G6">
-        <v>0.7000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s">
         <v>84</v>
@@ -3008,28 +3076,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D7">
-        <v>106.79</v>
+        <v>109.6</v>
       </c>
       <c r="E7">
-        <v>640.74</v>
+        <v>767.2</v>
       </c>
       <c r="F7">
-        <v>58.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="G7">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3037,28 +3105,28 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D8">
-        <v>105.2033333333333</v>
+        <v>107.69</v>
       </c>
       <c r="E8">
-        <v>631.22</v>
+        <v>753.83</v>
       </c>
       <c r="F8">
-        <v>53.6</v>
+        <v>41.8</v>
       </c>
       <c r="G8">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3066,28 +3134,28 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D9">
-        <v>108.7083333333333</v>
+        <v>108.9285714285714</v>
       </c>
       <c r="E9">
-        <v>652.25</v>
+        <v>762.5</v>
       </c>
       <c r="F9">
-        <v>27.2</v>
+        <v>14.6</v>
       </c>
       <c r="G9">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3095,28 +3163,28 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D10">
-        <v>102.0333333333333</v>
+        <v>103.6114285714286</v>
       </c>
       <c r="E10">
-        <v>612.2</v>
+        <v>725.2800000000001</v>
       </c>
       <c r="F10">
-        <v>3.6</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="G10">
-        <v>35.8</v>
+        <v>12.7</v>
       </c>
       <c r="H10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3124,28 +3192,28 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D11">
-        <v>89.61833333333334</v>
+        <v>82.44714285714285</v>
       </c>
       <c r="E11">
-        <v>537.71</v>
+        <v>577.13</v>
       </c>
       <c r="F11">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="G11">
-        <v>51.9</v>
+        <v>76.7</v>
       </c>
       <c r="H11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3160,19 +3228,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3180,19 +3248,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3200,19 +3268,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3220,19 +3288,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3243,16 +3311,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3260,19 +3328,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3280,19 +3348,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3300,19 +3368,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D8">
         <v>-5</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3320,19 +3388,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D9">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3343,16 +3411,16 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D10">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3363,16 +3431,16 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D11">
-        <v>-22</v>
+        <v>-32</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -3382,111 +3450,123 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>106</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>-11</v>
+      </c>
+      <c r="C2">
+        <v>-8</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
         <v>12</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>17</v>
       </c>
-      <c r="F2">
+      <c r="F3">
         <v>19</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>-11</v>
-      </c>
-      <c r="C3">
-        <v>-8</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
+      <c r="H3">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F3">
-        <v>8</v>
-      </c>
-      <c r="G3">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -3508,115 +3588,130 @@
       <c r="G5">
         <v>5</v>
       </c>
-      <c r="H5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
         <v>6</v>
       </c>
-      <c r="C6">
+      <c r="I6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D6">
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>-5</v>
+      </c>
+      <c r="D7">
+        <v>-1</v>
+      </c>
+      <c r="E7">
+        <v>-4</v>
+      </c>
+      <c r="F7">
+        <v>-4</v>
+      </c>
+      <c r="G7">
+        <v>-8</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="E6">
+      <c r="E8">
         <v>7</v>
       </c>
-      <c r="F6">
+      <c r="F8">
         <v>2</v>
       </c>
-      <c r="G6">
+      <c r="G8">
         <v>4</v>
       </c>
-      <c r="H6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
+      <c r="H8">
+        <v>-5</v>
+      </c>
+      <c r="I8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8">
+      <c r="C9">
         <v>1</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>-4</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>-12</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>-8</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>-5</v>
       </c>
-      <c r="H8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>-5</v>
-      </c>
-      <c r="D9">
-        <v>-1</v>
-      </c>
-      <c r="E9">
-        <v>-4</v>
-      </c>
-      <c r="F9">
-        <v>-4</v>
-      </c>
-      <c r="G9">
-        <v>-8</v>
-      </c>
-      <c r="H9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="H9">
+        <v>-6</v>
+      </c>
+      <c r="I9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -3638,11 +3733,14 @@
       <c r="G10">
         <v>-13</v>
       </c>
-      <c r="H10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="H10">
+        <v>-12</v>
+      </c>
+      <c r="I10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -3664,8 +3762,11 @@
       <c r="G11">
         <v>-22</v>
       </c>
-      <c r="H11" t="s">
-        <v>97</v>
+      <c r="H11">
+        <v>-32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Game of Yards! 2026.xlsx
+++ b/data/leagues/Game of Yards! 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="111">
   <si>
     <t>Groot-o-Matic</t>
   </si>
@@ -241,34 +241,28 @@
     <t>2-5</t>
   </si>
   <si>
-    <t>9.9-4.1-0.1</t>
+    <t>9.9-4.0</t>
   </si>
   <si>
     <t>8.5-5.4-0.1</t>
   </si>
   <si>
-    <t>8.7-5.2-0.1</t>
-  </si>
-  <si>
     <t>8.0-5.9-0.1</t>
   </si>
   <si>
-    <t>7.6-6.3-0.1</t>
-  </si>
-  <si>
-    <t>7.5-6.5-0.1</t>
-  </si>
-  <si>
-    <t>6.4-7.6-0.1</t>
-  </si>
-  <si>
-    <t>4.9-9.1-0.1</t>
+    <t>8.6-5.4-0.1</t>
+  </si>
+  <si>
+    <t>7.6-6.4-0.1</t>
+  </si>
+  <si>
+    <t>6.3-7.6-0.1</t>
   </si>
   <si>
     <t>4.8-9.1-0.1</t>
   </si>
   <si>
-    <t>3.5-10.5</t>
+    <t>3.5-10.4</t>
   </si>
   <si>
     <t>10-4</t>
@@ -278,9 +272,6 @@
   </si>
   <si>
     <t>8-6</t>
-  </si>
-  <si>
-    <t>7-7</t>
   </si>
   <si>
     <t>6-8</t>
@@ -1119,25 +1110,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1860,25 +1851,25 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>59.2</v>
+        <v>61.1</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>21.8</v>
       </c>
       <c r="D2">
-        <v>11.5</v>
+        <v>8.9</v>
       </c>
       <c r="E2">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="F2">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="G2">
         <v>0.9</v>
       </c>
       <c r="H2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1890,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>99.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1898,113 +1889,113 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>18.9</v>
+        <v>17.5</v>
       </c>
       <c r="C3">
-        <v>25.6</v>
+        <v>25.1</v>
       </c>
       <c r="D3">
-        <v>20.4</v>
+        <v>21.1</v>
       </c>
       <c r="E3">
-        <v>14.6</v>
+        <v>15.9</v>
       </c>
       <c r="F3">
-        <v>12.7</v>
+        <v>11.1</v>
       </c>
       <c r="G3">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="H3">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="I3">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J3">
         <v>0.2</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L3">
-        <v>97.09999999999999</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>8.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="C4">
-        <v>19.9</v>
+        <v>14.8</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="E4">
-        <v>19.3</v>
+        <v>15.8</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>17.8</v>
       </c>
       <c r="G4">
-        <v>10.7</v>
+        <v>14.6</v>
       </c>
       <c r="H4">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J4">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>93.2</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>17.9</v>
       </c>
       <c r="D5">
-        <v>17.6</v>
+        <v>19.9</v>
       </c>
       <c r="E5">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="F5">
-        <v>17.7</v>
+        <v>14.9</v>
       </c>
       <c r="G5">
-        <v>12.9</v>
+        <v>11.1</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J5">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="K5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>89.09999999999999</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2012,37 +2003,37 @@
         <v>0</v>
       </c>
       <c r="B6">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="C6">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="D6">
-        <v>14.2</v>
+        <v>15.1</v>
       </c>
       <c r="E6">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>17.9</v>
       </c>
       <c r="G6">
-        <v>14.7</v>
+        <v>16.1</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>10.6</v>
       </c>
       <c r="I6">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J6">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="K6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>83.5</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2050,37 +2041,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="C7">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="E7">
-        <v>12.7</v>
+        <v>16.2</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>23.1</v>
+        <v>18.2</v>
       </c>
       <c r="H7">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="I7">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="J7">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="K7">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L7">
-        <v>74.2</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2088,37 +2079,37 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="D8">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E8">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="F8">
-        <v>11.9</v>
+        <v>10.2</v>
       </c>
       <c r="G8">
-        <v>18.9</v>
+        <v>19.8</v>
       </c>
       <c r="H8">
-        <v>29.3</v>
+        <v>28.6</v>
       </c>
       <c r="I8">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="J8">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="L8">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2129,34 +2120,34 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D9">
         <v>0.4</v>
       </c>
       <c r="E9">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="F9">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="G9">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="H9">
-        <v>16.4</v>
+        <v>14.9</v>
       </c>
       <c r="I9">
-        <v>30</v>
+        <v>33.1</v>
       </c>
       <c r="J9">
-        <v>31.4</v>
+        <v>29.8</v>
       </c>
       <c r="K9">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
       <c r="L9">
-        <v>14.6</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2167,34 +2158,34 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E10">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F10">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="G10">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H10">
-        <v>12.9</v>
+        <v>12.2</v>
       </c>
       <c r="I10">
-        <v>29.4</v>
+        <v>28.8</v>
       </c>
       <c r="J10">
-        <v>38.4</v>
+        <v>36.7</v>
       </c>
       <c r="K10">
-        <v>12.7</v>
+        <v>13.6</v>
       </c>
       <c r="L10">
-        <v>6.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2211,28 +2202,28 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G11">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H11">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J11">
-        <v>15.8</v>
+        <v>17.8</v>
       </c>
       <c r="K11">
-        <v>76.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L11">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -2294,10 +2285,10 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>99.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="I2">
-        <v>99.90000000000001</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2323,10 +2314,10 @@
         <v>99.7</v>
       </c>
       <c r="H3">
-        <v>96.2</v>
+        <v>96</v>
       </c>
       <c r="I3">
-        <v>96.59999999999999</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2352,10 +2343,10 @@
         <v>83.89999999999999</v>
       </c>
       <c r="H4">
-        <v>89.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I4">
-        <v>92.30000000000001</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2381,10 +2372,10 @@
         <v>83</v>
       </c>
       <c r="H5">
-        <v>89.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I5">
-        <v>88.8</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2410,10 +2401,10 @@
         <v>90.8</v>
       </c>
       <c r="H6">
-        <v>87.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="I6">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2439,10 +2430,10 @@
         <v>54.40000000000001</v>
       </c>
       <c r="H7">
-        <v>72</v>
+        <v>78.7</v>
       </c>
       <c r="I7">
-        <v>76.2</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2468,10 +2459,10 @@
         <v>47.8</v>
       </c>
       <c r="H8">
-        <v>44.5</v>
+        <v>42.3</v>
       </c>
       <c r="I8">
-        <v>43.3</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2497,10 +2488,10 @@
         <v>32.7</v>
       </c>
       <c r="H9">
-        <v>13.6</v>
+        <v>15.3</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2526,10 +2517,10 @@
         <v>4.6</v>
       </c>
       <c r="H10">
-        <v>7.6</v>
+        <v>9.5</v>
       </c>
       <c r="I10">
-        <v>7.000000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2555,10 +2546,10 @@
         <v>3.1</v>
       </c>
       <c r="H11">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I11">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -2943,7 +2934,7 @@
         <v>892.3899999999999</v>
       </c>
       <c r="F2">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2952,7 +2943,7 @@
         <v>72</v>
       </c>
       <c r="I2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2972,36 +2963,36 @@
         <v>879.4399999999999</v>
       </c>
       <c r="F3">
-        <v>97.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H3" t="s">
         <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4">
-        <v>0.7142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D4">
-        <v>109.7485714285714</v>
+        <v>116.7857142857143</v>
       </c>
       <c r="E4">
-        <v>768.24</v>
+        <v>817.5</v>
       </c>
       <c r="F4">
-        <v>93.2</v>
+        <v>90.8</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3010,36 +3001,36 @@
         <v>74</v>
       </c>
       <c r="I4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D5">
-        <v>116.7857142857143</v>
+        <v>109.7485714285714</v>
       </c>
       <c r="E5">
-        <v>817.5</v>
+        <v>768.24</v>
       </c>
       <c r="F5">
-        <v>89.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
         <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3059,16 +3050,16 @@
         <v>813.64</v>
       </c>
       <c r="F6">
-        <v>83.5</v>
+        <v>82.5</v>
       </c>
       <c r="G6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>76</v>
       </c>
       <c r="I6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3088,16 +3079,16 @@
         <v>767.2</v>
       </c>
       <c r="F7">
-        <v>74.2</v>
+        <v>75.7</v>
       </c>
       <c r="G7">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3117,16 +3108,16 @@
         <v>753.83</v>
       </c>
       <c r="F8">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="G8">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3146,16 +3137,16 @@
         <v>762.5</v>
       </c>
       <c r="F9">
-        <v>14.6</v>
+        <v>13.1</v>
       </c>
       <c r="G9">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
       <c r="H9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3175,16 +3166,16 @@
         <v>725.2800000000001</v>
       </c>
       <c r="F10">
-        <v>6.600000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G10">
-        <v>12.7</v>
+        <v>13.6</v>
       </c>
       <c r="H10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3204,16 +3195,16 @@
         <v>577.13</v>
       </c>
       <c r="F11">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="G11">
-        <v>76.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3231,16 +3222,16 @@
         <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3260,7 +3251,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3280,7 +3271,7 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3300,7 +3291,7 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3320,7 +3311,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3340,7 +3331,7 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3360,7 +3351,7 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3380,7 +3371,7 @@
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3400,7 +3391,7 @@
         <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3420,7 +3411,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3440,7 +3431,7 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3455,28 +3446,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3505,7 +3496,7 @@
         <v>19</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3534,7 +3525,7 @@
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3563,7 +3554,7 @@
         <v>6</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3592,7 +3583,7 @@
         <v>6</v>
       </c>
       <c r="I5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3621,7 +3612,7 @@
         <v>6</v>
       </c>
       <c r="I6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3650,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3679,7 +3670,7 @@
         <v>-5</v>
       </c>
       <c r="I8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3708,7 +3699,7 @@
         <v>-6</v>
       </c>
       <c r="I9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3737,7 +3728,7 @@
         <v>-12</v>
       </c>
       <c r="I10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3766,7 +3757,7 @@
         <v>-32</v>
       </c>
       <c r="I11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
